--- a/docs/售后网络.xlsx
+++ b/docs/售后网络.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E149"/>
+  <dimension ref="A1:E150"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -1537,16 +1537,16 @@
         <v>华中区域</v>
       </c>
       <c r="B67" t="str">
-        <v>猛士襄阳襄州店</v>
+        <v>猛士汽车001武汉旗舰店</v>
       </c>
       <c r="C67" t="str">
         <v>湖北省</v>
       </c>
       <c r="D67" t="str">
-        <v>襄阳市</v>
+        <v>武汉市</v>
       </c>
       <c r="E67" t="str">
-        <v>襄州区</v>
+        <v>江岸区</v>
       </c>
     </row>
     <row r="68">
@@ -1554,16 +1554,16 @@
         <v>华中区域</v>
       </c>
       <c r="B68" t="str">
-        <v>猛士孝感授权服务中心</v>
+        <v>猛士襄阳襄州店</v>
       </c>
       <c r="C68" t="str">
         <v>湖北省</v>
       </c>
       <c r="D68" t="str">
-        <v>孝感市</v>
+        <v>襄阳市</v>
       </c>
       <c r="E68" t="str">
-        <v>孝南区</v>
+        <v>襄州区</v>
       </c>
     </row>
     <row r="69">
@@ -1571,16 +1571,16 @@
         <v>华中区域</v>
       </c>
       <c r="B69" t="str">
-        <v>猛士宜昌伍家岗店</v>
+        <v>猛士孝感授权服务中心</v>
       </c>
       <c r="C69" t="str">
         <v>湖北省</v>
       </c>
       <c r="D69" t="str">
-        <v>宜昌市</v>
+        <v>孝感市</v>
       </c>
       <c r="E69" t="str">
-        <v>伍家岗区</v>
+        <v>孝南区</v>
       </c>
     </row>
     <row r="70">
@@ -1588,16 +1588,16 @@
         <v>华中区域</v>
       </c>
       <c r="B70" t="str">
-        <v>猛士衡阳授权服务中心</v>
+        <v>猛士宜昌伍家岗店</v>
       </c>
       <c r="C70" t="str">
-        <v>湖南省</v>
+        <v>湖北省</v>
       </c>
       <c r="D70" t="str">
-        <v>衡阳市</v>
+        <v>宜昌市</v>
       </c>
       <c r="E70" t="str">
-        <v>蒸湘区</v>
+        <v>伍家岗区</v>
       </c>
     </row>
     <row r="71">
@@ -1605,16 +1605,16 @@
         <v>华中区域</v>
       </c>
       <c r="B71" t="str">
-        <v>猛士怀化鹤城店</v>
+        <v>猛士衡阳授权服务中心</v>
       </c>
       <c r="C71" t="str">
         <v>湖南省</v>
       </c>
       <c r="D71" t="str">
-        <v>怀化市</v>
+        <v>衡阳市</v>
       </c>
       <c r="E71" t="str">
-        <v>鹤城区</v>
+        <v>蒸湘区</v>
       </c>
     </row>
     <row r="72">
@@ -1622,16 +1622,16 @@
         <v>华中区域</v>
       </c>
       <c r="B72" t="str">
-        <v>猛士长沙开福店</v>
+        <v>猛士怀化鹤城店</v>
       </c>
       <c r="C72" t="str">
         <v>湖南省</v>
       </c>
       <c r="D72" t="str">
-        <v>长沙市</v>
+        <v>怀化市</v>
       </c>
       <c r="E72" t="str">
-        <v>开福区</v>
+        <v>鹤城区</v>
       </c>
     </row>
     <row r="73">
@@ -1639,7 +1639,7 @@
         <v>华中区域</v>
       </c>
       <c r="B73" t="str">
-        <v>猛士长沙中南店</v>
+        <v>猛士长沙开福店</v>
       </c>
       <c r="C73" t="str">
         <v>湖南省</v>
@@ -1648,7 +1648,7 @@
         <v>长沙市</v>
       </c>
       <c r="E73" t="str">
-        <v>长沙县</v>
+        <v>开福区</v>
       </c>
     </row>
     <row r="74">
@@ -1656,16 +1656,16 @@
         <v>华中区域</v>
       </c>
       <c r="B74" t="str">
-        <v>猛士南昌授权服务中心</v>
+        <v>猛士长沙中南店</v>
       </c>
       <c r="C74" t="str">
-        <v>江西省</v>
+        <v>湖南省</v>
       </c>
       <c r="D74" t="str">
-        <v>南昌市</v>
+        <v>长沙市</v>
       </c>
       <c r="E74" t="str">
-        <v>青山湖区</v>
+        <v>长沙县</v>
       </c>
     </row>
     <row r="75">
@@ -1673,33 +1673,33 @@
         <v>华中区域</v>
       </c>
       <c r="B75" t="str">
-        <v>猛士上饶月亮湾店</v>
+        <v>猛士南昌授权服务中心</v>
       </c>
       <c r="C75" t="str">
         <v>江西省</v>
       </c>
       <c r="D75" t="str">
-        <v>上饶市</v>
+        <v>南昌市</v>
       </c>
       <c r="E75" t="str">
-        <v>广信区</v>
+        <v>青山湖区</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>华南区域</v>
+        <v>华中区域</v>
       </c>
       <c r="B76" t="str">
-        <v>猛士福州仓山店</v>
+        <v>猛士上饶月亮湾店</v>
       </c>
       <c r="C76" t="str">
-        <v>福建省</v>
+        <v>江西省</v>
       </c>
       <c r="D76" t="str">
-        <v>福州市</v>
+        <v>上饶市</v>
       </c>
       <c r="E76" t="str">
-        <v>仓山区</v>
+        <v>广信区</v>
       </c>
     </row>
     <row r="77">
@@ -1707,16 +1707,16 @@
         <v>华南区域</v>
       </c>
       <c r="B77" t="str">
-        <v>猛士宁德授权服务中心</v>
+        <v>猛士福州仓山店</v>
       </c>
       <c r="C77" t="str">
         <v>福建省</v>
       </c>
       <c r="D77" t="str">
-        <v>宁德市</v>
+        <v>福州市</v>
       </c>
       <c r="E77" t="str">
-        <v>蕉城区</v>
+        <v>仓山区</v>
       </c>
     </row>
     <row r="78">
@@ -1724,16 +1724,16 @@
         <v>华南区域</v>
       </c>
       <c r="B78" t="str">
-        <v>猛士泉州鲤城店</v>
+        <v>猛士宁德授权服务中心</v>
       </c>
       <c r="C78" t="str">
         <v>福建省</v>
       </c>
       <c r="D78" t="str">
-        <v>泉州市</v>
+        <v>宁德市</v>
       </c>
       <c r="E78" t="str">
-        <v>鲤城区</v>
+        <v>蕉城区</v>
       </c>
     </row>
     <row r="79">
@@ -1741,16 +1741,16 @@
         <v>华南区域</v>
       </c>
       <c r="B79" t="str">
-        <v>猛士厦门翔安店</v>
+        <v>猛士泉州鲤城店</v>
       </c>
       <c r="C79" t="str">
         <v>福建省</v>
       </c>
       <c r="D79" t="str">
-        <v>厦门市</v>
+        <v>泉州市</v>
       </c>
       <c r="E79" t="str">
-        <v>翔安区</v>
+        <v>鲤城区</v>
       </c>
     </row>
     <row r="80">
@@ -1758,16 +1758,16 @@
         <v>华南区域</v>
       </c>
       <c r="B80" t="str">
-        <v>猛士东莞寮步店</v>
+        <v>猛士厦门翔安店</v>
       </c>
       <c r="C80" t="str">
-        <v>广东省</v>
+        <v>福建省</v>
       </c>
       <c r="D80" t="str">
-        <v>东莞市</v>
+        <v>厦门市</v>
       </c>
       <c r="E80" t="str">
-        <v>寮步镇</v>
+        <v>翔安区</v>
       </c>
     </row>
     <row r="81">
@@ -1775,7 +1775,7 @@
         <v>华南区域</v>
       </c>
       <c r="B81" t="str">
-        <v>猛士东莞塘厦店</v>
+        <v>猛士东莞寮步店</v>
       </c>
       <c r="C81" t="str">
         <v>广东省</v>
@@ -1784,7 +1784,7 @@
         <v>东莞市</v>
       </c>
       <c r="E81" t="str">
-        <v>塘厦镇</v>
+        <v>寮步镇</v>
       </c>
     </row>
     <row r="82">
@@ -1792,16 +1792,16 @@
         <v>华南区域</v>
       </c>
       <c r="B82" t="str">
-        <v>猛士佛山禅城店</v>
+        <v>猛士东莞塘厦店</v>
       </c>
       <c r="C82" t="str">
         <v>广东省</v>
       </c>
       <c r="D82" t="str">
-        <v>佛山市</v>
+        <v>东莞市</v>
       </c>
       <c r="E82" t="str">
-        <v>禅城区</v>
+        <v>塘厦镇</v>
       </c>
     </row>
     <row r="83">
@@ -1809,7 +1809,7 @@
         <v>华南区域</v>
       </c>
       <c r="B83" t="str">
-        <v>猛士佛山海八路店</v>
+        <v>猛士佛山禅城店</v>
       </c>
       <c r="C83" t="str">
         <v>广东省</v>
@@ -1818,7 +1818,7 @@
         <v>佛山市</v>
       </c>
       <c r="E83" t="str">
-        <v>南海区</v>
+        <v>禅城区</v>
       </c>
     </row>
     <row r="84">
@@ -1826,16 +1826,16 @@
         <v>华南区域</v>
       </c>
       <c r="B84" t="str">
-        <v>猛士广州番禺店</v>
+        <v>猛士佛山海八路店</v>
       </c>
       <c r="C84" t="str">
         <v>广东省</v>
       </c>
       <c r="D84" t="str">
-        <v>广州市</v>
+        <v>佛山市</v>
       </c>
       <c r="E84" t="str">
-        <v>番禺区</v>
+        <v>南海区</v>
       </c>
     </row>
     <row r="85">
@@ -1843,7 +1843,7 @@
         <v>华南区域</v>
       </c>
       <c r="B85" t="str">
-        <v>猛士广州龙洞店</v>
+        <v>猛士广州番禺店</v>
       </c>
       <c r="C85" t="str">
         <v>广东省</v>
@@ -1852,7 +1852,7 @@
         <v>广州市</v>
       </c>
       <c r="E85" t="str">
-        <v>天河区</v>
+        <v>番禺区</v>
       </c>
     </row>
     <row r="86">
@@ -1860,16 +1860,16 @@
         <v>华南区域</v>
       </c>
       <c r="B86" t="str">
-        <v>猛士惠州惠城店</v>
+        <v>猛士广州龙洞店</v>
       </c>
       <c r="C86" t="str">
         <v>广东省</v>
       </c>
       <c r="D86" t="str">
-        <v>惠州市</v>
+        <v>广州市</v>
       </c>
       <c r="E86" t="str">
-        <v>惠城区</v>
+        <v>天河区</v>
       </c>
     </row>
     <row r="87">
@@ -1877,16 +1877,16 @@
         <v>华南区域</v>
       </c>
       <c r="B87" t="str">
-        <v>猛士梅州梅江店</v>
+        <v>猛士惠州惠城店</v>
       </c>
       <c r="C87" t="str">
         <v>广东省</v>
       </c>
       <c r="D87" t="str">
-        <v>梅州市</v>
+        <v>惠州市</v>
       </c>
       <c r="E87" t="str">
-        <v>梅江区</v>
+        <v>惠城区</v>
       </c>
     </row>
     <row r="88">
@@ -1894,16 +1894,16 @@
         <v>华南区域</v>
       </c>
       <c r="B88" t="str">
-        <v>猛士汕头高新店</v>
+        <v>猛士梅州梅江店</v>
       </c>
       <c r="C88" t="str">
         <v>广东省</v>
       </c>
       <c r="D88" t="str">
-        <v>汕头市</v>
+        <v>梅州市</v>
       </c>
       <c r="E88" t="str">
-        <v>金平区</v>
+        <v>梅江区</v>
       </c>
     </row>
     <row r="89">
@@ -1911,16 +1911,16 @@
         <v>华南区域</v>
       </c>
       <c r="B89" t="str">
-        <v>猛士深圳宝安店</v>
+        <v>猛士汕头高新店</v>
       </c>
       <c r="C89" t="str">
         <v>广东省</v>
       </c>
       <c r="D89" t="str">
-        <v>深圳市</v>
+        <v>汕头市</v>
       </c>
       <c r="E89" t="str">
-        <v>宝安区</v>
+        <v>金平区</v>
       </c>
     </row>
     <row r="90">
@@ -1928,16 +1928,16 @@
         <v>华南区域</v>
       </c>
       <c r="B90" t="str">
-        <v>猛士湛江授权服务中心</v>
+        <v>猛士深圳宝安店</v>
       </c>
       <c r="C90" t="str">
         <v>广东省</v>
       </c>
       <c r="D90" t="str">
-        <v>湛江市</v>
+        <v>深圳市</v>
       </c>
       <c r="E90" t="str">
-        <v>赤坎区</v>
+        <v>宝安区</v>
       </c>
     </row>
     <row r="91">
@@ -1945,16 +1945,16 @@
         <v>华南区域</v>
       </c>
       <c r="B91" t="str">
-        <v>猛士中山小榄店</v>
+        <v>猛士湛江授权服务中心</v>
       </c>
       <c r="C91" t="str">
         <v>广东省</v>
       </c>
       <c r="D91" t="str">
-        <v>中山市</v>
+        <v>湛江市</v>
       </c>
       <c r="E91" t="str">
-        <v>小榄镇</v>
+        <v>赤坎区</v>
       </c>
     </row>
     <row r="92">
@@ -1962,16 +1962,16 @@
         <v>华南区域</v>
       </c>
       <c r="B92" t="str">
-        <v>猛士南宁江南店</v>
+        <v>猛士中山小榄店</v>
       </c>
       <c r="C92" t="str">
-        <v>广西壮族自治区</v>
+        <v>广东省</v>
       </c>
       <c r="D92" t="str">
-        <v>南宁市</v>
+        <v>中山市</v>
       </c>
       <c r="E92" t="str">
-        <v>江南区</v>
+        <v>小榄镇</v>
       </c>
     </row>
     <row r="93">
@@ -1979,16 +1979,16 @@
         <v>华南区域</v>
       </c>
       <c r="B93" t="str">
-        <v>猛士海口美兰店</v>
+        <v>猛士南宁江南店</v>
       </c>
       <c r="C93" t="str">
-        <v>海南省</v>
+        <v>广西壮族自治区</v>
       </c>
       <c r="D93" t="str">
-        <v>海口市</v>
+        <v>南宁市</v>
       </c>
       <c r="E93" t="str">
-        <v>美兰区</v>
+        <v>江南区</v>
       </c>
     </row>
     <row r="94">
@@ -1996,33 +1996,33 @@
         <v>华南区域</v>
       </c>
       <c r="B94" t="str">
-        <v>猛士三亚授权服务中心</v>
+        <v>猛士海口美兰店</v>
       </c>
       <c r="C94" t="str">
         <v>海南省</v>
       </c>
       <c r="D94" t="str">
-        <v>三亚市</v>
+        <v>海口市</v>
       </c>
       <c r="E94" t="str">
-        <v>吉阳区</v>
+        <v>美兰区</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>西南区域</v>
+        <v>华南区域</v>
       </c>
       <c r="B95" t="str">
-        <v>猛士重庆九龙坡店</v>
+        <v>猛士三亚授权服务中心</v>
       </c>
       <c r="C95" t="str">
-        <v>重庆市</v>
+        <v>海南省</v>
       </c>
       <c r="D95" t="str">
-        <v>重庆市</v>
+        <v>三亚市</v>
       </c>
       <c r="E95" t="str">
-        <v>九龙坡区</v>
+        <v>吉阳区</v>
       </c>
     </row>
     <row r="96">
@@ -2030,7 +2030,7 @@
         <v>西南区域</v>
       </c>
       <c r="B96" t="str">
-        <v>猛士重庆海峡路店</v>
+        <v>猛士重庆九龙坡店</v>
       </c>
       <c r="C96" t="str">
         <v>重庆市</v>
@@ -2039,7 +2039,7 @@
         <v>重庆市</v>
       </c>
       <c r="E96" t="str">
-        <v>南岸区</v>
+        <v>九龙坡区</v>
       </c>
     </row>
     <row r="97">
@@ -2047,7 +2047,7 @@
         <v>西南区域</v>
       </c>
       <c r="B97" t="str">
-        <v>猛士重庆渝北店</v>
+        <v>猛士重庆海峡路店</v>
       </c>
       <c r="C97" t="str">
         <v>重庆市</v>
@@ -2056,7 +2056,7 @@
         <v>重庆市</v>
       </c>
       <c r="E97" t="str">
-        <v>渝北区</v>
+        <v>南岸区</v>
       </c>
     </row>
     <row r="98">
@@ -2064,16 +2064,16 @@
         <v>西南区域</v>
       </c>
       <c r="B98" t="str">
-        <v>猛士贵阳观山湖店</v>
+        <v>猛士重庆渝北店</v>
       </c>
       <c r="C98" t="str">
-        <v>贵州省</v>
+        <v>重庆市</v>
       </c>
       <c r="D98" t="str">
-        <v>贵阳市</v>
+        <v>重庆市</v>
       </c>
       <c r="E98" t="str">
-        <v>观山湖区</v>
+        <v>渝北区</v>
       </c>
     </row>
     <row r="99">
@@ -2081,7 +2081,7 @@
         <v>西南区域</v>
       </c>
       <c r="B99" t="str">
-        <v>猛士贵阳花溪店</v>
+        <v>猛士贵阳观山湖店</v>
       </c>
       <c r="C99" t="str">
         <v>贵州省</v>
@@ -2090,7 +2090,7 @@
         <v>贵阳市</v>
       </c>
       <c r="E99" t="str">
-        <v>花溪区</v>
+        <v>观山湖区</v>
       </c>
     </row>
     <row r="100">
@@ -2098,16 +2098,16 @@
         <v>西南区域</v>
       </c>
       <c r="B100" t="str">
-        <v>猛士遵义授权服务中心</v>
+        <v>猛士贵阳花溪店</v>
       </c>
       <c r="C100" t="str">
         <v>贵州省</v>
       </c>
       <c r="D100" t="str">
-        <v>遵义市</v>
+        <v>贵阳市</v>
       </c>
       <c r="E100" t="str">
-        <v>汇川区</v>
+        <v>花溪区</v>
       </c>
     </row>
     <row r="101">
@@ -2115,16 +2115,16 @@
         <v>西南区域</v>
       </c>
       <c r="B101" t="str">
-        <v>猛士成都天府新区店</v>
+        <v>猛士遵义授权服务中心</v>
       </c>
       <c r="C101" t="str">
-        <v>四川省</v>
+        <v>贵州省</v>
       </c>
       <c r="D101" t="str">
-        <v>成都市</v>
+        <v>遵义市</v>
       </c>
       <c r="E101" t="str">
-        <v>双流区</v>
+        <v>汇川区</v>
       </c>
     </row>
     <row r="102">
@@ -2132,7 +2132,7 @@
         <v>西南区域</v>
       </c>
       <c r="B102" t="str">
-        <v>猛士成都授权服务中心</v>
+        <v>猛士成都天府新区店</v>
       </c>
       <c r="C102" t="str">
         <v>四川省</v>
@@ -2141,7 +2141,7 @@
         <v>成都市</v>
       </c>
       <c r="E102" t="str">
-        <v>武侯区</v>
+        <v>双流区</v>
       </c>
     </row>
     <row r="103">
@@ -2149,16 +2149,16 @@
         <v>西南区域</v>
       </c>
       <c r="B103" t="str">
-        <v>猛士乐山高新店</v>
+        <v>猛士成都授权服务中心</v>
       </c>
       <c r="C103" t="str">
         <v>四川省</v>
       </c>
       <c r="D103" t="str">
-        <v>乐山市</v>
+        <v>成都市</v>
       </c>
       <c r="E103" t="str">
-        <v>市中区</v>
+        <v>武侯区</v>
       </c>
     </row>
     <row r="104">
@@ -2166,16 +2166,16 @@
         <v>西南区域</v>
       </c>
       <c r="B104" t="str">
-        <v>猛士西昌安宁店</v>
+        <v>猛士乐山高新店</v>
       </c>
       <c r="C104" t="str">
         <v>四川省</v>
       </c>
       <c r="D104" t="str">
-        <v>凉山彝族自治州</v>
+        <v>乐山市</v>
       </c>
       <c r="E104" t="str">
-        <v>西昌市</v>
+        <v>市中区</v>
       </c>
     </row>
     <row r="105">
@@ -2183,16 +2183,16 @@
         <v>西南区域</v>
       </c>
       <c r="B105" t="str">
-        <v>猛士泸州龙马潭店</v>
+        <v>猛士西昌安宁店</v>
       </c>
       <c r="C105" t="str">
         <v>四川省</v>
       </c>
       <c r="D105" t="str">
-        <v>泸州市</v>
+        <v>凉山彝族自治州</v>
       </c>
       <c r="E105" t="str">
-        <v>龙马潭区</v>
+        <v>西昌市</v>
       </c>
     </row>
     <row r="106">
@@ -2200,16 +2200,16 @@
         <v>西南区域</v>
       </c>
       <c r="B106" t="str">
-        <v>猛士眉山东坡店</v>
+        <v>猛士泸州龙马潭店</v>
       </c>
       <c r="C106" t="str">
         <v>四川省</v>
       </c>
       <c r="D106" t="str">
-        <v>眉山市</v>
+        <v>泸州市</v>
       </c>
       <c r="E106" t="str">
-        <v>东坡区</v>
+        <v>龙马潭区</v>
       </c>
     </row>
     <row r="107">
@@ -2217,16 +2217,16 @@
         <v>西南区域</v>
       </c>
       <c r="B107" t="str">
-        <v>猛士绵阳涪城店</v>
+        <v>猛士眉山东坡店</v>
       </c>
       <c r="C107" t="str">
         <v>四川省</v>
       </c>
       <c r="D107" t="str">
-        <v>绵阳市</v>
+        <v>眉山市</v>
       </c>
       <c r="E107" t="str">
-        <v>涪城区</v>
+        <v>东坡区</v>
       </c>
     </row>
     <row r="108">
@@ -2234,16 +2234,16 @@
         <v>西南区域</v>
       </c>
       <c r="B108" t="str">
-        <v>猛士南充高坪店</v>
+        <v>猛士绵阳涪城店</v>
       </c>
       <c r="C108" t="str">
         <v>四川省</v>
       </c>
       <c r="D108" t="str">
-        <v>南充市</v>
+        <v>绵阳市</v>
       </c>
       <c r="E108" t="str">
-        <v>高坪区</v>
+        <v>涪城区</v>
       </c>
     </row>
     <row r="109">
@@ -2251,16 +2251,16 @@
         <v>西南区域</v>
       </c>
       <c r="B109" t="str">
-        <v>猛士攀枝花天骏店</v>
+        <v>猛士南充高坪店</v>
       </c>
       <c r="C109" t="str">
         <v>四川省</v>
       </c>
       <c r="D109" t="str">
-        <v>攀枝花市</v>
+        <v>南充市</v>
       </c>
       <c r="E109" t="str">
-        <v>西区</v>
+        <v>高坪区</v>
       </c>
     </row>
     <row r="110">
@@ -2268,16 +2268,16 @@
         <v>西南区域</v>
       </c>
       <c r="B110" t="str">
-        <v>猛士宜宾临港店</v>
+        <v>猛士攀枝花天骏店</v>
       </c>
       <c r="C110" t="str">
         <v>四川省</v>
       </c>
       <c r="D110" t="str">
-        <v>宜宾市</v>
+        <v>攀枝花市</v>
       </c>
       <c r="E110" t="str">
-        <v>翠屏区</v>
+        <v>西区</v>
       </c>
     </row>
     <row r="111">
@@ -2285,16 +2285,16 @@
         <v>西南区域</v>
       </c>
       <c r="B111" t="str">
-        <v>猛士拉萨授权服务中心</v>
+        <v>猛士宜宾临港店</v>
       </c>
       <c r="C111" t="str">
-        <v>西藏自治区</v>
+        <v>四川省</v>
       </c>
       <c r="D111" t="str">
-        <v>拉萨市</v>
+        <v>宜宾市</v>
       </c>
       <c r="E111" t="str">
-        <v>城关区</v>
+        <v>翠屏区</v>
       </c>
     </row>
     <row r="112">
@@ -2302,16 +2302,16 @@
         <v>西南区域</v>
       </c>
       <c r="B112" t="str">
-        <v>猛士林芝授权服务中心</v>
+        <v>猛士拉萨授权服务中心</v>
       </c>
       <c r="C112" t="str">
         <v>西藏自治区</v>
       </c>
       <c r="D112" t="str">
-        <v>林芝市</v>
+        <v>拉萨市</v>
       </c>
       <c r="E112" t="str">
-        <v>巴宜区</v>
+        <v>城关区</v>
       </c>
     </row>
     <row r="113">
@@ -2319,16 +2319,16 @@
         <v>西南区域</v>
       </c>
       <c r="B113" t="str">
-        <v>猛士大理授权服务中心</v>
+        <v>猛士林芝授权服务中心</v>
       </c>
       <c r="C113" t="str">
-        <v>云南省</v>
+        <v>西藏自治区</v>
       </c>
       <c r="D113" t="str">
-        <v>大理白族自治州</v>
+        <v>林芝市</v>
       </c>
       <c r="E113" t="str">
-        <v>大理市</v>
+        <v>巴宜区</v>
       </c>
     </row>
     <row r="114">
@@ -2336,16 +2336,16 @@
         <v>西南区域</v>
       </c>
       <c r="B114" t="str">
-        <v>猛士昆明西山店</v>
+        <v>猛士大理授权服务中心</v>
       </c>
       <c r="C114" t="str">
         <v>云南省</v>
       </c>
       <c r="D114" t="str">
-        <v>昆明市</v>
+        <v>大理白族自治州</v>
       </c>
       <c r="E114" t="str">
-        <v>西山区</v>
+        <v>大理市</v>
       </c>
     </row>
     <row r="115">
@@ -2353,16 +2353,16 @@
         <v>西南区域</v>
       </c>
       <c r="B115" t="str">
-        <v>猛士丽江授权服务中心</v>
+        <v>猛士昆明西山店</v>
       </c>
       <c r="C115" t="str">
         <v>云南省</v>
       </c>
       <c r="D115" t="str">
-        <v>丽江市</v>
+        <v>昆明市</v>
       </c>
       <c r="E115" t="str">
-        <v>玉龙纳西族自治县</v>
+        <v>西山区</v>
       </c>
     </row>
     <row r="116">
@@ -2370,33 +2370,33 @@
         <v>西南区域</v>
       </c>
       <c r="B116" t="str">
-        <v>猛士西双版纳授权服务中心</v>
+        <v>猛士丽江授权服务中心</v>
       </c>
       <c r="C116" t="str">
         <v>云南省</v>
       </c>
       <c r="D116" t="str">
-        <v>西双版纳傣族自治州</v>
+        <v>丽江市</v>
       </c>
       <c r="E116" t="str">
-        <v>景洪市</v>
+        <v>玉龙纳西族自治县</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>西北区域</v>
+        <v>西南区域</v>
       </c>
       <c r="B117" t="str">
-        <v>猛士敦煌授权服务中心</v>
+        <v>猛士西双版纳授权服务中心</v>
       </c>
       <c r="C117" t="str">
-        <v>甘肃省</v>
+        <v>云南省</v>
       </c>
       <c r="D117" t="str">
-        <v>酒泉市</v>
+        <v>西双版纳傣族自治州</v>
       </c>
       <c r="E117" t="str">
-        <v>敦煌市</v>
+        <v>景洪市</v>
       </c>
     </row>
     <row r="118">
@@ -2404,16 +2404,16 @@
         <v>西北区域</v>
       </c>
       <c r="B118" t="str">
-        <v>猛士兰州安宁店</v>
+        <v>猛士敦煌授权服务中心</v>
       </c>
       <c r="C118" t="str">
         <v>甘肃省</v>
       </c>
       <c r="D118" t="str">
-        <v>兰州市</v>
+        <v>酒泉市</v>
       </c>
       <c r="E118" t="str">
-        <v>安宁区</v>
+        <v>敦煌市</v>
       </c>
     </row>
     <row r="119">
@@ -2421,16 +2421,16 @@
         <v>西北区域</v>
       </c>
       <c r="B119" t="str">
-        <v>猛士庆阳授权服务中心</v>
+        <v>猛士兰州安宁店</v>
       </c>
       <c r="C119" t="str">
         <v>甘肃省</v>
       </c>
       <c r="D119" t="str">
-        <v>庆阳市</v>
+        <v>兰州市</v>
       </c>
       <c r="E119" t="str">
-        <v>西峰区</v>
+        <v>安宁区</v>
       </c>
     </row>
     <row r="120">
@@ -2438,16 +2438,16 @@
         <v>西北区域</v>
       </c>
       <c r="B120" t="str">
-        <v>猛士银川德胜店</v>
+        <v>猛士庆阳授权服务中心</v>
       </c>
       <c r="C120" t="str">
-        <v>宁夏回族自治区</v>
+        <v>甘肃省</v>
       </c>
       <c r="D120" t="str">
-        <v>银川市</v>
+        <v>庆阳市</v>
       </c>
       <c r="E120" t="str">
-        <v>贺兰县</v>
+        <v>西峰区</v>
       </c>
     </row>
     <row r="121">
@@ -2455,16 +2455,16 @@
         <v>西北区域</v>
       </c>
       <c r="B121" t="str">
-        <v>猛士西宁城东店</v>
+        <v>猛士银川德胜店</v>
       </c>
       <c r="C121" t="str">
-        <v>青海省</v>
+        <v>宁夏回族自治区</v>
       </c>
       <c r="D121" t="str">
-        <v>西宁市</v>
+        <v>银川市</v>
       </c>
       <c r="E121" t="str">
-        <v>城东区</v>
+        <v>贺兰县</v>
       </c>
     </row>
     <row r="122">
@@ -2472,16 +2472,16 @@
         <v>西北区域</v>
       </c>
       <c r="B122" t="str">
-        <v>猛士宝鸡平安路店</v>
+        <v>猛士西宁城东店</v>
       </c>
       <c r="C122" t="str">
-        <v>陕西省</v>
+        <v>青海省</v>
       </c>
       <c r="D122" t="str">
-        <v>宝鸡市</v>
+        <v>西宁市</v>
       </c>
       <c r="E122" t="str">
-        <v>渭滨区</v>
+        <v>城东区</v>
       </c>
     </row>
     <row r="123">
@@ -2489,16 +2489,16 @@
         <v>西北区域</v>
       </c>
       <c r="B123" t="str">
-        <v>猛士西安浐灞店</v>
+        <v>猛士宝鸡平安路店</v>
       </c>
       <c r="C123" t="str">
         <v>陕西省</v>
       </c>
       <c r="D123" t="str">
-        <v>西安市</v>
+        <v>宝鸡市</v>
       </c>
       <c r="E123" t="str">
-        <v>灞桥区</v>
+        <v>渭滨区</v>
       </c>
     </row>
     <row r="124">
@@ -2506,7 +2506,7 @@
         <v>西北区域</v>
       </c>
       <c r="B124" t="str">
-        <v>猛士西安未央店</v>
+        <v>猛士西安浐灞店</v>
       </c>
       <c r="C124" t="str">
         <v>陕西省</v>
@@ -2515,7 +2515,7 @@
         <v>西安市</v>
       </c>
       <c r="E124" t="str">
-        <v>未央区</v>
+        <v>灞桥区</v>
       </c>
     </row>
     <row r="125">
@@ -2523,7 +2523,7 @@
         <v>西北区域</v>
       </c>
       <c r="B125" t="str">
-        <v>猛士西安经开店</v>
+        <v>猛士西安未央店</v>
       </c>
       <c r="C125" t="str">
         <v>陕西省</v>
@@ -2540,16 +2540,16 @@
         <v>西北区域</v>
       </c>
       <c r="B126" t="str">
-        <v>猛士榆林草海则店</v>
+        <v>猛士西安经开店</v>
       </c>
       <c r="C126" t="str">
         <v>陕西省</v>
       </c>
       <c r="D126" t="str">
-        <v>榆林市</v>
+        <v>西安市</v>
       </c>
       <c r="E126" t="str">
-        <v>横山区</v>
+        <v>未央区</v>
       </c>
     </row>
     <row r="127">
@@ -2557,16 +2557,16 @@
         <v>西北区域</v>
       </c>
       <c r="B127" t="str">
-        <v>猛士乌鲁木齐店</v>
+        <v>猛士榆林草海则店</v>
       </c>
       <c r="C127" t="str">
-        <v>新疆维吾尔自治区</v>
+        <v>陕西省</v>
       </c>
       <c r="D127" t="str">
-        <v>乌鲁木齐市</v>
+        <v>榆林市</v>
       </c>
       <c r="E127" t="str">
-        <v>水磨沟区</v>
+        <v>横山区</v>
       </c>
     </row>
     <row r="128">
@@ -2574,7 +2574,7 @@
         <v>西北区域</v>
       </c>
       <c r="B128" t="str">
-        <v>猛士乌鲁木齐喀什西路店</v>
+        <v>猛士乌鲁木齐店</v>
       </c>
       <c r="C128" t="str">
         <v>新疆维吾尔自治区</v>
@@ -2583,24 +2583,24 @@
         <v>乌鲁木齐市</v>
       </c>
       <c r="E128" t="str">
-        <v>头屯河区</v>
+        <v>水磨沟区</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>东北区域</v>
+        <v>西北区域</v>
       </c>
       <c r="B129" t="str">
-        <v>猛士大庆让胡路授权服务中心</v>
+        <v>猛士乌鲁木齐喀什西路店</v>
       </c>
       <c r="C129" t="str">
-        <v>黑龙江省</v>
+        <v>新疆维吾尔自治区</v>
       </c>
       <c r="D129" t="str">
-        <v>大庆市</v>
+        <v>乌鲁木齐市</v>
       </c>
       <c r="E129" t="str">
-        <v>让胡路区</v>
+        <v>头屯河区</v>
       </c>
     </row>
     <row r="130">
@@ -2608,16 +2608,16 @@
         <v>东北区域</v>
       </c>
       <c r="B130" t="str">
-        <v>猛士哈尔滨香坊店</v>
+        <v>猛士大庆让胡路授权服务中心</v>
       </c>
       <c r="C130" t="str">
         <v>黑龙江省</v>
       </c>
       <c r="D130" t="str">
-        <v>哈尔滨市</v>
+        <v>大庆市</v>
       </c>
       <c r="E130" t="str">
-        <v>香坊区</v>
+        <v>让胡路区</v>
       </c>
     </row>
     <row r="131">
@@ -2625,16 +2625,16 @@
         <v>东北区域</v>
       </c>
       <c r="B131" t="str">
-        <v>猛士北安授权服务中心</v>
+        <v>猛士哈尔滨香坊店</v>
       </c>
       <c r="C131" t="str">
         <v>黑龙江省</v>
       </c>
       <c r="D131" t="str">
-        <v>黑河市</v>
+        <v>哈尔滨市</v>
       </c>
       <c r="E131" t="str">
-        <v>北安市</v>
+        <v>香坊区</v>
       </c>
     </row>
     <row r="132">
@@ -2642,16 +2642,16 @@
         <v>东北区域</v>
       </c>
       <c r="B132" t="str">
-        <v>猛士佳木斯授权服务中心</v>
+        <v>猛士北安授权服务中心</v>
       </c>
       <c r="C132" t="str">
         <v>黑龙江省</v>
       </c>
       <c r="D132" t="str">
-        <v>佳木斯市</v>
+        <v>黑河市</v>
       </c>
       <c r="E132" t="str">
-        <v>郊区</v>
+        <v>北安市</v>
       </c>
     </row>
     <row r="133">
@@ -2659,16 +2659,16 @@
         <v>东北区域</v>
       </c>
       <c r="B133" t="str">
-        <v>猛士牡丹江授权服务中心</v>
+        <v>猛士佳木斯授权服务中心</v>
       </c>
       <c r="C133" t="str">
         <v>黑龙江省</v>
       </c>
       <c r="D133" t="str">
-        <v>牡丹江市</v>
+        <v>佳木斯市</v>
       </c>
       <c r="E133" t="str">
-        <v>阳明区</v>
+        <v>郊区</v>
       </c>
     </row>
     <row r="134">
@@ -2676,16 +2676,16 @@
         <v>东北区域</v>
       </c>
       <c r="B134" t="str">
-        <v>猛士齐齐哈尔铁锋授权服务中心</v>
+        <v>猛士牡丹江授权服务中心</v>
       </c>
       <c r="C134" t="str">
         <v>黑龙江省</v>
       </c>
       <c r="D134" t="str">
-        <v>齐齐哈尔市</v>
+        <v>牡丹江市</v>
       </c>
       <c r="E134" t="str">
-        <v>铁锋区</v>
+        <v>阳明区</v>
       </c>
     </row>
     <row r="135">
@@ -2693,16 +2693,16 @@
         <v>东北区域</v>
       </c>
       <c r="B135" t="str">
-        <v>猛士松原授权服务中心</v>
+        <v>猛士齐齐哈尔铁锋授权服务中心</v>
       </c>
       <c r="C135" t="str">
-        <v>吉林省</v>
+        <v>黑龙江省</v>
       </c>
       <c r="D135" t="str">
-        <v>松原市</v>
+        <v>齐齐哈尔市</v>
       </c>
       <c r="E135" t="str">
-        <v>宁江区</v>
+        <v>铁锋区</v>
       </c>
     </row>
     <row r="136">
@@ -2710,16 +2710,16 @@
         <v>东北区域</v>
       </c>
       <c r="B136" t="str">
-        <v>猛士长春经开店</v>
+        <v>猛士松原授权服务中心</v>
       </c>
       <c r="C136" t="str">
         <v>吉林省</v>
       </c>
       <c r="D136" t="str">
-        <v>长春市</v>
+        <v>松原市</v>
       </c>
       <c r="E136" t="str">
-        <v>二道区</v>
+        <v>宁江区</v>
       </c>
     </row>
     <row r="137">
@@ -2727,16 +2727,16 @@
         <v>东北区域</v>
       </c>
       <c r="B137" t="str">
-        <v>猛士大连华北路店</v>
+        <v>猛士长春经开店</v>
       </c>
       <c r="C137" t="str">
-        <v>辽宁省</v>
+        <v>吉林省</v>
       </c>
       <c r="D137" t="str">
-        <v>大连市</v>
+        <v>长春市</v>
       </c>
       <c r="E137" t="str">
-        <v>甘井子区</v>
+        <v>二道区</v>
       </c>
     </row>
     <row r="138">
@@ -2744,16 +2744,16 @@
         <v>东北区域</v>
       </c>
       <c r="B138" t="str">
-        <v>猛士沈阳店</v>
+        <v>猛士大连华北路店</v>
       </c>
       <c r="C138" t="str">
         <v>辽宁省</v>
       </c>
       <c r="D138" t="str">
-        <v>沈阳市</v>
+        <v>大连市</v>
       </c>
       <c r="E138" t="str">
-        <v>浑南区</v>
+        <v>甘井子区</v>
       </c>
     </row>
     <row r="139">
@@ -2761,7 +2761,7 @@
         <v>东北区域</v>
       </c>
       <c r="B139" t="str">
-        <v>猛士沈阳沈河店</v>
+        <v>猛士沈阳店</v>
       </c>
       <c r="C139" t="str">
         <v>辽宁省</v>
@@ -2770,7 +2770,7 @@
         <v>沈阳市</v>
       </c>
       <c r="E139" t="str">
-        <v>沈河区</v>
+        <v>浑南区</v>
       </c>
     </row>
     <row r="140">
@@ -2778,16 +2778,16 @@
         <v>东北区域</v>
       </c>
       <c r="B140" t="str">
-        <v>猛士包头九原店</v>
+        <v>猛士沈阳沈河店</v>
       </c>
       <c r="C140" t="str">
-        <v>内蒙古自治区</v>
+        <v>辽宁省</v>
       </c>
       <c r="D140" t="str">
-        <v>包头市</v>
+        <v>沈阳市</v>
       </c>
       <c r="E140" t="str">
-        <v>九原区</v>
+        <v>沈河区</v>
       </c>
     </row>
     <row r="141">
@@ -2795,16 +2795,16 @@
         <v>东北区域</v>
       </c>
       <c r="B141" t="str">
-        <v>猛士赤峰红山店</v>
+        <v>猛士包头九原店</v>
       </c>
       <c r="C141" t="str">
         <v>内蒙古自治区</v>
       </c>
       <c r="D141" t="str">
-        <v>赤峰市</v>
+        <v>包头市</v>
       </c>
       <c r="E141" t="str">
-        <v>红山区</v>
+        <v>九原区</v>
       </c>
     </row>
     <row r="142">
@@ -2812,16 +2812,16 @@
         <v>东北区域</v>
       </c>
       <c r="B142" t="str">
-        <v>猛士鄂尔多斯东胜店</v>
+        <v>猛士赤峰红山店</v>
       </c>
       <c r="C142" t="str">
         <v>内蒙古自治区</v>
       </c>
       <c r="D142" t="str">
-        <v>鄂尔多斯市</v>
+        <v>赤峰市</v>
       </c>
       <c r="E142" t="str">
-        <v>东胜区</v>
+        <v>红山区</v>
       </c>
     </row>
     <row r="143">
@@ -2829,16 +2829,16 @@
         <v>东北区域</v>
       </c>
       <c r="B143" t="str">
-        <v>猛士呼和浩特海西路店</v>
+        <v>猛士鄂尔多斯东胜店</v>
       </c>
       <c r="C143" t="str">
         <v>内蒙古自治区</v>
       </c>
       <c r="D143" t="str">
-        <v>呼和浩特市</v>
+        <v>鄂尔多斯市</v>
       </c>
       <c r="E143" t="str">
-        <v>回民区</v>
+        <v>东胜区</v>
       </c>
     </row>
     <row r="144">
@@ -2846,16 +2846,16 @@
         <v>东北区域</v>
       </c>
       <c r="B144" t="str">
-        <v>猛士呼伦贝尔汽车城店</v>
+        <v>猛士呼和浩特海西路店</v>
       </c>
       <c r="C144" t="str">
         <v>内蒙古自治区</v>
       </c>
       <c r="D144" t="str">
-        <v>呼伦贝尔市</v>
+        <v>呼和浩特市</v>
       </c>
       <c r="E144" t="str">
-        <v>鄂温克族自治旗</v>
+        <v>回民区</v>
       </c>
     </row>
     <row r="145">
@@ -2863,16 +2863,16 @@
         <v>东北区域</v>
       </c>
       <c r="B145" t="str">
-        <v>猛士通辽万林店</v>
+        <v>猛士呼伦贝尔汽车城店</v>
       </c>
       <c r="C145" t="str">
         <v>内蒙古自治区</v>
       </c>
       <c r="D145" t="str">
-        <v>通辽市</v>
+        <v>呼伦贝尔市</v>
       </c>
       <c r="E145" t="str">
-        <v>科尔沁区</v>
+        <v>鄂温克族自治旗</v>
       </c>
     </row>
     <row r="146">
@@ -2880,16 +2880,16 @@
         <v>东北区域</v>
       </c>
       <c r="B146" t="str">
-        <v>猛士大同经开店</v>
+        <v>猛士通辽万林店</v>
       </c>
       <c r="C146" t="str">
-        <v>山西省</v>
+        <v>内蒙古自治区</v>
       </c>
       <c r="D146" t="str">
-        <v>大同市</v>
+        <v>通辽市</v>
       </c>
       <c r="E146" t="str">
-        <v>云州区</v>
+        <v>科尔沁区</v>
       </c>
     </row>
     <row r="147">
@@ -2897,16 +2897,16 @@
         <v>东北区域</v>
       </c>
       <c r="B147" t="str">
-        <v>猛士晋城路宝店</v>
+        <v>猛士大同经开店</v>
       </c>
       <c r="C147" t="str">
         <v>山西省</v>
       </c>
       <c r="D147" t="str">
-        <v>晋城市</v>
+        <v>大同市</v>
       </c>
       <c r="E147" t="str">
-        <v>泽州县</v>
+        <v>云州区</v>
       </c>
     </row>
     <row r="148">
@@ -2914,16 +2914,16 @@
         <v>东北区域</v>
       </c>
       <c r="B148" t="str">
-        <v>猛士太原龙城店</v>
+        <v>猛士晋城路宝店</v>
       </c>
       <c r="C148" t="str">
         <v>山西省</v>
       </c>
       <c r="D148" t="str">
-        <v>太原市</v>
+        <v>晋城市</v>
       </c>
       <c r="E148" t="str">
-        <v>小店区</v>
+        <v>泽州县</v>
       </c>
     </row>
     <row r="149">
@@ -2931,21 +2931,38 @@
         <v>东北区域</v>
       </c>
       <c r="B149" t="str">
-        <v>猛士长治潞州店</v>
+        <v>猛士太原龙城店</v>
       </c>
       <c r="C149" t="str">
         <v>山西省</v>
       </c>
       <c r="D149" t="str">
+        <v>太原市</v>
+      </c>
+      <c r="E149" t="str">
+        <v>小店区</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>东北区域</v>
+      </c>
+      <c r="B150" t="str">
+        <v>猛士长治潞州店</v>
+      </c>
+      <c r="C150" t="str">
+        <v>山西省</v>
+      </c>
+      <c r="D150" t="str">
         <v>长治市</v>
       </c>
-      <c r="E149" t="str">
+      <c r="E150" t="str">
         <v>潞州区</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E149"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E150"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/售后网络.xlsx
+++ b/docs/售后网络.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E150"/>
+  <dimension ref="A1:E148"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -500,7 +500,7 @@
         <v>华东区域</v>
       </c>
       <c r="B6" t="str">
-        <v>猛士泰州授权服务中心</v>
+        <v>猛士泰州高港区店</v>
       </c>
       <c r="C6" t="str">
         <v>江苏省</v>
@@ -551,7 +551,7 @@
         <v>华东区域</v>
       </c>
       <c r="B9" t="str">
-        <v>猛士盐城授权服务中心</v>
+        <v>猛士盐城亭湖区店</v>
       </c>
       <c r="C9" t="str">
         <v>江苏省</v>
@@ -1231,7 +1231,7 @@
         <v>华中区域</v>
       </c>
       <c r="B49" t="str">
-        <v>猛士安阳授权服务中心</v>
+        <v>猛士安阳安阳县店</v>
       </c>
       <c r="C49" t="str">
         <v>河南省</v>
@@ -1248,7 +1248,7 @@
         <v>华中区域</v>
       </c>
       <c r="B50" t="str">
-        <v>猛士鹤壁授权服务中心</v>
+        <v>猛士鹤壁淇滨区店</v>
       </c>
       <c r="C50" t="str">
         <v>河南省</v>
@@ -1265,7 +1265,7 @@
         <v>华中区域</v>
       </c>
       <c r="B51" t="str">
-        <v>猛士开封授权服务中心</v>
+        <v>猛士开封龙亭区店</v>
       </c>
       <c r="C51" t="str">
         <v>河南省</v>
@@ -1299,7 +1299,7 @@
         <v>华中区域</v>
       </c>
       <c r="B53" t="str">
-        <v>猛士漯河授权服务中心</v>
+        <v>猛士漯河源汇区店</v>
       </c>
       <c r="C53" t="str">
         <v>河南省</v>
@@ -1316,7 +1316,7 @@
         <v>华中区域</v>
       </c>
       <c r="B54" t="str">
-        <v>猛士平顶山授权服务中心</v>
+        <v>猛士平顶山卫东区店</v>
       </c>
       <c r="C54" t="str">
         <v>河南省</v>
@@ -1333,7 +1333,7 @@
         <v>华中区域</v>
       </c>
       <c r="B55" t="str">
-        <v>猛士濮阳授权服务中心</v>
+        <v>猛士濮阳华龙区店</v>
       </c>
       <c r="C55" t="str">
         <v>河南省</v>
@@ -1350,7 +1350,7 @@
         <v>华中区域</v>
       </c>
       <c r="B56" t="str">
-        <v>猛士商丘授权服务中心</v>
+        <v>猛士商丘梁园区店</v>
       </c>
       <c r="C56" t="str">
         <v>河南省</v>
@@ -1384,7 +1384,7 @@
         <v>华中区域</v>
       </c>
       <c r="B58" t="str">
-        <v>猛士许昌授权服务中心</v>
+        <v>猛士许昌魏都区店</v>
       </c>
       <c r="C58" t="str">
         <v>河南省</v>
@@ -1452,7 +1452,7 @@
         <v>华中区域</v>
       </c>
       <c r="B62" t="str">
-        <v>猛士驻马店授权服务中心</v>
+        <v>猛士驻马店上蔡县店</v>
       </c>
       <c r="C62" t="str">
         <v>河南省</v>
@@ -1469,7 +1469,7 @@
         <v>华中区域</v>
       </c>
       <c r="B63" t="str">
-        <v>猛士恩施授权服务中心</v>
+        <v>猛士恩施店</v>
       </c>
       <c r="C63" t="str">
         <v>湖北省</v>
@@ -1503,7 +1503,7 @@
         <v>华中区域</v>
       </c>
       <c r="B65" t="str">
-        <v>猛士武汉汉阳授权服务中心</v>
+        <v>猛士武汉汉阳区店</v>
       </c>
       <c r="C65" t="str">
         <v>湖北省</v>
@@ -1571,7 +1571,7 @@
         <v>华中区域</v>
       </c>
       <c r="B69" t="str">
-        <v>猛士孝感授权服务中心</v>
+        <v>猛士孝感孝南区店</v>
       </c>
       <c r="C69" t="str">
         <v>湖北省</v>
@@ -1605,7 +1605,7 @@
         <v>华中区域</v>
       </c>
       <c r="B71" t="str">
-        <v>猛士衡阳授权服务中心</v>
+        <v>猛士衡阳蒸湘区店</v>
       </c>
       <c r="C71" t="str">
         <v>湖南省</v>
@@ -1673,7 +1673,7 @@
         <v>华中区域</v>
       </c>
       <c r="B75" t="str">
-        <v>猛士南昌授权服务中心</v>
+        <v>猛士南昌青山湖区店</v>
       </c>
       <c r="C75" t="str">
         <v>江西省</v>
@@ -1724,7 +1724,7 @@
         <v>华南区域</v>
       </c>
       <c r="B78" t="str">
-        <v>猛士宁德授权服务中心</v>
+        <v>猛士宁德蕉城区店</v>
       </c>
       <c r="C78" t="str">
         <v>福建省</v>
@@ -1775,7 +1775,7 @@
         <v>华南区域</v>
       </c>
       <c r="B81" t="str">
-        <v>猛士东莞寮步店</v>
+        <v>猛士东莞塘厦店</v>
       </c>
       <c r="C81" t="str">
         <v>广东省</v>
@@ -1784,7 +1784,7 @@
         <v>东莞市</v>
       </c>
       <c r="E81" t="str">
-        <v>寮步镇</v>
+        <v>塘厦镇</v>
       </c>
     </row>
     <row r="82">
@@ -1792,16 +1792,16 @@
         <v>华南区域</v>
       </c>
       <c r="B82" t="str">
-        <v>猛士东莞塘厦店</v>
+        <v>猛士佛山禅城店</v>
       </c>
       <c r="C82" t="str">
         <v>广东省</v>
       </c>
       <c r="D82" t="str">
-        <v>东莞市</v>
+        <v>佛山市</v>
       </c>
       <c r="E82" t="str">
-        <v>塘厦镇</v>
+        <v>禅城区</v>
       </c>
     </row>
     <row r="83">
@@ -1809,7 +1809,7 @@
         <v>华南区域</v>
       </c>
       <c r="B83" t="str">
-        <v>猛士佛山禅城店</v>
+        <v>猛士佛山海八路店</v>
       </c>
       <c r="C83" t="str">
         <v>广东省</v>
@@ -1818,7 +1818,7 @@
         <v>佛山市</v>
       </c>
       <c r="E83" t="str">
-        <v>禅城区</v>
+        <v>南海区</v>
       </c>
     </row>
     <row r="84">
@@ -1826,16 +1826,16 @@
         <v>华南区域</v>
       </c>
       <c r="B84" t="str">
-        <v>猛士佛山海八路店</v>
+        <v>猛士广州番禺店</v>
       </c>
       <c r="C84" t="str">
         <v>广东省</v>
       </c>
       <c r="D84" t="str">
-        <v>佛山市</v>
+        <v>广州市</v>
       </c>
       <c r="E84" t="str">
-        <v>南海区</v>
+        <v>番禺区</v>
       </c>
     </row>
     <row r="85">
@@ -1843,7 +1843,7 @@
         <v>华南区域</v>
       </c>
       <c r="B85" t="str">
-        <v>猛士广州番禺店</v>
+        <v>猛士广州龙洞店</v>
       </c>
       <c r="C85" t="str">
         <v>广东省</v>
@@ -1852,7 +1852,7 @@
         <v>广州市</v>
       </c>
       <c r="E85" t="str">
-        <v>番禺区</v>
+        <v>天河区</v>
       </c>
     </row>
     <row r="86">
@@ -1860,16 +1860,16 @@
         <v>华南区域</v>
       </c>
       <c r="B86" t="str">
-        <v>猛士广州龙洞店</v>
+        <v>猛士惠州惠城店</v>
       </c>
       <c r="C86" t="str">
         <v>广东省</v>
       </c>
       <c r="D86" t="str">
-        <v>广州市</v>
+        <v>惠州市</v>
       </c>
       <c r="E86" t="str">
-        <v>天河区</v>
+        <v>惠城区</v>
       </c>
     </row>
     <row r="87">
@@ -1877,16 +1877,16 @@
         <v>华南区域</v>
       </c>
       <c r="B87" t="str">
-        <v>猛士惠州惠城店</v>
+        <v>猛士梅州梅江店</v>
       </c>
       <c r="C87" t="str">
         <v>广东省</v>
       </c>
       <c r="D87" t="str">
-        <v>惠州市</v>
+        <v>梅州市</v>
       </c>
       <c r="E87" t="str">
-        <v>惠城区</v>
+        <v>梅江区</v>
       </c>
     </row>
     <row r="88">
@@ -1894,16 +1894,16 @@
         <v>华南区域</v>
       </c>
       <c r="B88" t="str">
-        <v>猛士梅州梅江店</v>
+        <v>猛士汕头高新店</v>
       </c>
       <c r="C88" t="str">
         <v>广东省</v>
       </c>
       <c r="D88" t="str">
-        <v>梅州市</v>
+        <v>汕头市</v>
       </c>
       <c r="E88" t="str">
-        <v>梅江区</v>
+        <v>金平区</v>
       </c>
     </row>
     <row r="89">
@@ -1911,16 +1911,16 @@
         <v>华南区域</v>
       </c>
       <c r="B89" t="str">
-        <v>猛士汕头高新店</v>
+        <v>猛士深圳宝安店</v>
       </c>
       <c r="C89" t="str">
         <v>广东省</v>
       </c>
       <c r="D89" t="str">
-        <v>汕头市</v>
+        <v>深圳市</v>
       </c>
       <c r="E89" t="str">
-        <v>金平区</v>
+        <v>宝安区</v>
       </c>
     </row>
     <row r="90">
@@ -1928,16 +1928,16 @@
         <v>华南区域</v>
       </c>
       <c r="B90" t="str">
-        <v>猛士深圳宝安店</v>
+        <v>猛士湛江赤坎区店</v>
       </c>
       <c r="C90" t="str">
         <v>广东省</v>
       </c>
       <c r="D90" t="str">
-        <v>深圳市</v>
+        <v>湛江市</v>
       </c>
       <c r="E90" t="str">
-        <v>宝安区</v>
+        <v>赤坎区</v>
       </c>
     </row>
     <row r="91">
@@ -1945,16 +1945,16 @@
         <v>华南区域</v>
       </c>
       <c r="B91" t="str">
-        <v>猛士湛江授权服务中心</v>
+        <v>猛士中山小榄店</v>
       </c>
       <c r="C91" t="str">
         <v>广东省</v>
       </c>
       <c r="D91" t="str">
-        <v>湛江市</v>
+        <v>中山市</v>
       </c>
       <c r="E91" t="str">
-        <v>赤坎区</v>
+        <v>小榄镇</v>
       </c>
     </row>
     <row r="92">
@@ -1962,16 +1962,16 @@
         <v>华南区域</v>
       </c>
       <c r="B92" t="str">
-        <v>猛士中山小榄店</v>
+        <v>猛士南宁江南店</v>
       </c>
       <c r="C92" t="str">
-        <v>广东省</v>
+        <v>广西壮族自治区</v>
       </c>
       <c r="D92" t="str">
-        <v>中山市</v>
+        <v>南宁市</v>
       </c>
       <c r="E92" t="str">
-        <v>小榄镇</v>
+        <v>江南区</v>
       </c>
     </row>
     <row r="93">
@@ -1979,16 +1979,16 @@
         <v>华南区域</v>
       </c>
       <c r="B93" t="str">
-        <v>猛士南宁江南店</v>
+        <v>猛士海口美兰店</v>
       </c>
       <c r="C93" t="str">
-        <v>广西壮族自治区</v>
+        <v>海南省</v>
       </c>
       <c r="D93" t="str">
-        <v>南宁市</v>
+        <v>海口市</v>
       </c>
       <c r="E93" t="str">
-        <v>江南区</v>
+        <v>美兰区</v>
       </c>
     </row>
     <row r="94">
@@ -1996,33 +1996,33 @@
         <v>华南区域</v>
       </c>
       <c r="B94" t="str">
-        <v>猛士海口美兰店</v>
+        <v>猛士三亚吉阳区店</v>
       </c>
       <c r="C94" t="str">
         <v>海南省</v>
       </c>
       <c r="D94" t="str">
-        <v>海口市</v>
+        <v>三亚市</v>
       </c>
       <c r="E94" t="str">
-        <v>美兰区</v>
+        <v>吉阳区</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>华南区域</v>
+        <v>西南区域</v>
       </c>
       <c r="B95" t="str">
-        <v>猛士三亚授权服务中心</v>
+        <v>猛士重庆九龙坡店</v>
       </c>
       <c r="C95" t="str">
-        <v>海南省</v>
+        <v>重庆市</v>
       </c>
       <c r="D95" t="str">
-        <v>三亚市</v>
+        <v>重庆市</v>
       </c>
       <c r="E95" t="str">
-        <v>吉阳区</v>
+        <v>九龙坡区</v>
       </c>
     </row>
     <row r="96">
@@ -2030,7 +2030,7 @@
         <v>西南区域</v>
       </c>
       <c r="B96" t="str">
-        <v>猛士重庆九龙坡店</v>
+        <v>猛士重庆海峡路店</v>
       </c>
       <c r="C96" t="str">
         <v>重庆市</v>
@@ -2039,7 +2039,7 @@
         <v>重庆市</v>
       </c>
       <c r="E96" t="str">
-        <v>九龙坡区</v>
+        <v>南岸区</v>
       </c>
     </row>
     <row r="97">
@@ -2047,7 +2047,7 @@
         <v>西南区域</v>
       </c>
       <c r="B97" t="str">
-        <v>猛士重庆海峡路店</v>
+        <v>猛士重庆渝北店</v>
       </c>
       <c r="C97" t="str">
         <v>重庆市</v>
@@ -2056,7 +2056,7 @@
         <v>重庆市</v>
       </c>
       <c r="E97" t="str">
-        <v>南岸区</v>
+        <v>渝北区</v>
       </c>
     </row>
     <row r="98">
@@ -2064,16 +2064,16 @@
         <v>西南区域</v>
       </c>
       <c r="B98" t="str">
-        <v>猛士重庆渝北店</v>
+        <v>猛士贵阳观山湖店</v>
       </c>
       <c r="C98" t="str">
-        <v>重庆市</v>
+        <v>贵州省</v>
       </c>
       <c r="D98" t="str">
-        <v>重庆市</v>
+        <v>贵阳市</v>
       </c>
       <c r="E98" t="str">
-        <v>渝北区</v>
+        <v>观山湖区</v>
       </c>
     </row>
     <row r="99">
@@ -2081,7 +2081,7 @@
         <v>西南区域</v>
       </c>
       <c r="B99" t="str">
-        <v>猛士贵阳观山湖店</v>
+        <v>猛士贵阳花溪店</v>
       </c>
       <c r="C99" t="str">
         <v>贵州省</v>
@@ -2090,7 +2090,7 @@
         <v>贵阳市</v>
       </c>
       <c r="E99" t="str">
-        <v>观山湖区</v>
+        <v>花溪区</v>
       </c>
     </row>
     <row r="100">
@@ -2098,16 +2098,16 @@
         <v>西南区域</v>
       </c>
       <c r="B100" t="str">
-        <v>猛士贵阳花溪店</v>
+        <v>猛士遵义汇川区店</v>
       </c>
       <c r="C100" t="str">
         <v>贵州省</v>
       </c>
       <c r="D100" t="str">
-        <v>贵阳市</v>
+        <v>遵义市</v>
       </c>
       <c r="E100" t="str">
-        <v>花溪区</v>
+        <v>汇川区</v>
       </c>
     </row>
     <row r="101">
@@ -2115,16 +2115,16 @@
         <v>西南区域</v>
       </c>
       <c r="B101" t="str">
-        <v>猛士遵义授权服务中心</v>
+        <v>猛士成都天府新区店</v>
       </c>
       <c r="C101" t="str">
-        <v>贵州省</v>
+        <v>四川省</v>
       </c>
       <c r="D101" t="str">
-        <v>遵义市</v>
+        <v>成都市</v>
       </c>
       <c r="E101" t="str">
-        <v>汇川区</v>
+        <v>双流区</v>
       </c>
     </row>
     <row r="102">
@@ -2132,7 +2132,7 @@
         <v>西南区域</v>
       </c>
       <c r="B102" t="str">
-        <v>猛士成都天府新区店</v>
+        <v>猛士成都武侯区店</v>
       </c>
       <c r="C102" t="str">
         <v>四川省</v>
@@ -2141,7 +2141,7 @@
         <v>成都市</v>
       </c>
       <c r="E102" t="str">
-        <v>双流区</v>
+        <v>武侯区</v>
       </c>
     </row>
     <row r="103">
@@ -2149,16 +2149,16 @@
         <v>西南区域</v>
       </c>
       <c r="B103" t="str">
-        <v>猛士成都授权服务中心</v>
+        <v>猛士乐山高新店</v>
       </c>
       <c r="C103" t="str">
         <v>四川省</v>
       </c>
       <c r="D103" t="str">
-        <v>成都市</v>
+        <v>乐山市</v>
       </c>
       <c r="E103" t="str">
-        <v>武侯区</v>
+        <v>市中区</v>
       </c>
     </row>
     <row r="104">
@@ -2166,16 +2166,16 @@
         <v>西南区域</v>
       </c>
       <c r="B104" t="str">
-        <v>猛士乐山高新店</v>
+        <v>猛士西昌安宁店</v>
       </c>
       <c r="C104" t="str">
         <v>四川省</v>
       </c>
       <c r="D104" t="str">
-        <v>乐山市</v>
+        <v>凉山彝族自治州</v>
       </c>
       <c r="E104" t="str">
-        <v>市中区</v>
+        <v>西昌市</v>
       </c>
     </row>
     <row r="105">
@@ -2183,16 +2183,16 @@
         <v>西南区域</v>
       </c>
       <c r="B105" t="str">
-        <v>猛士西昌安宁店</v>
+        <v>猛士泸州龙马潭店</v>
       </c>
       <c r="C105" t="str">
         <v>四川省</v>
       </c>
       <c r="D105" t="str">
-        <v>凉山彝族自治州</v>
+        <v>泸州市</v>
       </c>
       <c r="E105" t="str">
-        <v>西昌市</v>
+        <v>龙马潭区</v>
       </c>
     </row>
     <row r="106">
@@ -2200,16 +2200,16 @@
         <v>西南区域</v>
       </c>
       <c r="B106" t="str">
-        <v>猛士泸州龙马潭店</v>
+        <v>猛士眉山东坡店</v>
       </c>
       <c r="C106" t="str">
         <v>四川省</v>
       </c>
       <c r="D106" t="str">
-        <v>泸州市</v>
+        <v>眉山市</v>
       </c>
       <c r="E106" t="str">
-        <v>龙马潭区</v>
+        <v>东坡区</v>
       </c>
     </row>
     <row r="107">
@@ -2217,16 +2217,16 @@
         <v>西南区域</v>
       </c>
       <c r="B107" t="str">
-        <v>猛士眉山东坡店</v>
+        <v>猛士绵阳涪城店</v>
       </c>
       <c r="C107" t="str">
         <v>四川省</v>
       </c>
       <c r="D107" t="str">
-        <v>眉山市</v>
+        <v>绵阳市</v>
       </c>
       <c r="E107" t="str">
-        <v>东坡区</v>
+        <v>涪城区</v>
       </c>
     </row>
     <row r="108">
@@ -2234,16 +2234,16 @@
         <v>西南区域</v>
       </c>
       <c r="B108" t="str">
-        <v>猛士绵阳涪城店</v>
+        <v>猛士南充高坪店</v>
       </c>
       <c r="C108" t="str">
         <v>四川省</v>
       </c>
       <c r="D108" t="str">
-        <v>绵阳市</v>
+        <v>南充市</v>
       </c>
       <c r="E108" t="str">
-        <v>涪城区</v>
+        <v>高坪区</v>
       </c>
     </row>
     <row r="109">
@@ -2251,16 +2251,16 @@
         <v>西南区域</v>
       </c>
       <c r="B109" t="str">
-        <v>猛士南充高坪店</v>
+        <v>猛士攀枝花天骏店</v>
       </c>
       <c r="C109" t="str">
         <v>四川省</v>
       </c>
       <c r="D109" t="str">
-        <v>南充市</v>
+        <v>攀枝花市</v>
       </c>
       <c r="E109" t="str">
-        <v>高坪区</v>
+        <v>西区</v>
       </c>
     </row>
     <row r="110">
@@ -2268,16 +2268,16 @@
         <v>西南区域</v>
       </c>
       <c r="B110" t="str">
-        <v>猛士攀枝花天骏店</v>
+        <v>猛士宜宾临港店</v>
       </c>
       <c r="C110" t="str">
         <v>四川省</v>
       </c>
       <c r="D110" t="str">
-        <v>攀枝花市</v>
+        <v>宜宾市</v>
       </c>
       <c r="E110" t="str">
-        <v>西区</v>
+        <v>翠屏区</v>
       </c>
     </row>
     <row r="111">
@@ -2285,16 +2285,16 @@
         <v>西南区域</v>
       </c>
       <c r="B111" t="str">
-        <v>猛士宜宾临港店</v>
+        <v>猛士拉萨城关区店</v>
       </c>
       <c r="C111" t="str">
-        <v>四川省</v>
+        <v>西藏自治区</v>
       </c>
       <c r="D111" t="str">
-        <v>宜宾市</v>
+        <v>拉萨市</v>
       </c>
       <c r="E111" t="str">
-        <v>翠屏区</v>
+        <v>城关区</v>
       </c>
     </row>
     <row r="112">
@@ -2302,16 +2302,16 @@
         <v>西南区域</v>
       </c>
       <c r="B112" t="str">
-        <v>猛士拉萨授权服务中心</v>
+        <v>猛士林芝巴宜区店</v>
       </c>
       <c r="C112" t="str">
         <v>西藏自治区</v>
       </c>
       <c r="D112" t="str">
-        <v>拉萨市</v>
+        <v>林芝市</v>
       </c>
       <c r="E112" t="str">
-        <v>城关区</v>
+        <v>巴宜区</v>
       </c>
     </row>
     <row r="113">
@@ -2319,16 +2319,16 @@
         <v>西南区域</v>
       </c>
       <c r="B113" t="str">
-        <v>猛士林芝授权服务中心</v>
+        <v>猛士大理店</v>
       </c>
       <c r="C113" t="str">
-        <v>西藏自治区</v>
+        <v>云南省</v>
       </c>
       <c r="D113" t="str">
-        <v>林芝市</v>
+        <v>大理白族自治州</v>
       </c>
       <c r="E113" t="str">
-        <v>巴宜区</v>
+        <v>大理市</v>
       </c>
     </row>
     <row r="114">
@@ -2336,16 +2336,16 @@
         <v>西南区域</v>
       </c>
       <c r="B114" t="str">
-        <v>猛士大理授权服务中心</v>
+        <v>猛士昆明西山店</v>
       </c>
       <c r="C114" t="str">
         <v>云南省</v>
       </c>
       <c r="D114" t="str">
-        <v>大理白族自治州</v>
+        <v>昆明市</v>
       </c>
       <c r="E114" t="str">
-        <v>大理市</v>
+        <v>西山区</v>
       </c>
     </row>
     <row r="115">
@@ -2353,50 +2353,50 @@
         <v>西南区域</v>
       </c>
       <c r="B115" t="str">
-        <v>猛士昆明西山店</v>
+        <v>猛士西双版纳景洪店</v>
       </c>
       <c r="C115" t="str">
         <v>云南省</v>
       </c>
       <c r="D115" t="str">
-        <v>昆明市</v>
+        <v>西双版纳傣族自治州</v>
       </c>
       <c r="E115" t="str">
-        <v>西山区</v>
+        <v>景洪市</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>西南区域</v>
+        <v>西北区域</v>
       </c>
       <c r="B116" t="str">
-        <v>猛士丽江授权服务中心</v>
+        <v>猛士敦煌店</v>
       </c>
       <c r="C116" t="str">
-        <v>云南省</v>
+        <v>甘肃省</v>
       </c>
       <c r="D116" t="str">
-        <v>丽江市</v>
+        <v>酒泉市</v>
       </c>
       <c r="E116" t="str">
-        <v>玉龙纳西族自治县</v>
+        <v>敦煌市</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>西南区域</v>
+        <v>西北区域</v>
       </c>
       <c r="B117" t="str">
-        <v>猛士西双版纳授权服务中心</v>
+        <v>猛士兰州安宁店</v>
       </c>
       <c r="C117" t="str">
-        <v>云南省</v>
+        <v>甘肃省</v>
       </c>
       <c r="D117" t="str">
-        <v>西双版纳傣族自治州</v>
+        <v>兰州市</v>
       </c>
       <c r="E117" t="str">
-        <v>景洪市</v>
+        <v>安宁区</v>
       </c>
     </row>
     <row r="118">
@@ -2404,16 +2404,16 @@
         <v>西北区域</v>
       </c>
       <c r="B118" t="str">
-        <v>猛士敦煌授权服务中心</v>
+        <v>猛士庆阳西峰区店</v>
       </c>
       <c r="C118" t="str">
         <v>甘肃省</v>
       </c>
       <c r="D118" t="str">
-        <v>酒泉市</v>
+        <v>庆阳市</v>
       </c>
       <c r="E118" t="str">
-        <v>敦煌市</v>
+        <v>西峰区</v>
       </c>
     </row>
     <row r="119">
@@ -2421,16 +2421,16 @@
         <v>西北区域</v>
       </c>
       <c r="B119" t="str">
-        <v>猛士兰州安宁店</v>
+        <v>猛士银川德胜店</v>
       </c>
       <c r="C119" t="str">
-        <v>甘肃省</v>
+        <v>宁夏回族自治区</v>
       </c>
       <c r="D119" t="str">
-        <v>兰州市</v>
+        <v>银川市</v>
       </c>
       <c r="E119" t="str">
-        <v>安宁区</v>
+        <v>贺兰县</v>
       </c>
     </row>
     <row r="120">
@@ -2438,16 +2438,16 @@
         <v>西北区域</v>
       </c>
       <c r="B120" t="str">
-        <v>猛士庆阳授权服务中心</v>
+        <v>猛士西宁城东店</v>
       </c>
       <c r="C120" t="str">
-        <v>甘肃省</v>
+        <v>青海省</v>
       </c>
       <c r="D120" t="str">
-        <v>庆阳市</v>
+        <v>西宁市</v>
       </c>
       <c r="E120" t="str">
-        <v>西峰区</v>
+        <v>城东区</v>
       </c>
     </row>
     <row r="121">
@@ -2455,16 +2455,16 @@
         <v>西北区域</v>
       </c>
       <c r="B121" t="str">
-        <v>猛士银川德胜店</v>
+        <v>猛士宝鸡平安路店</v>
       </c>
       <c r="C121" t="str">
-        <v>宁夏回族自治区</v>
+        <v>陕西省</v>
       </c>
       <c r="D121" t="str">
-        <v>银川市</v>
+        <v>宝鸡市</v>
       </c>
       <c r="E121" t="str">
-        <v>贺兰县</v>
+        <v>渭滨区</v>
       </c>
     </row>
     <row r="122">
@@ -2472,16 +2472,16 @@
         <v>西北区域</v>
       </c>
       <c r="B122" t="str">
-        <v>猛士西宁城东店</v>
+        <v>猛士西安浐灞店</v>
       </c>
       <c r="C122" t="str">
-        <v>青海省</v>
+        <v>陕西省</v>
       </c>
       <c r="D122" t="str">
-        <v>西宁市</v>
+        <v>西安市</v>
       </c>
       <c r="E122" t="str">
-        <v>城东区</v>
+        <v>灞桥区</v>
       </c>
     </row>
     <row r="123">
@@ -2489,16 +2489,16 @@
         <v>西北区域</v>
       </c>
       <c r="B123" t="str">
-        <v>猛士宝鸡平安路店</v>
+        <v>猛士西安未央店</v>
       </c>
       <c r="C123" t="str">
         <v>陕西省</v>
       </c>
       <c r="D123" t="str">
-        <v>宝鸡市</v>
+        <v>西安市</v>
       </c>
       <c r="E123" t="str">
-        <v>渭滨区</v>
+        <v>未央区</v>
       </c>
     </row>
     <row r="124">
@@ -2506,7 +2506,7 @@
         <v>西北区域</v>
       </c>
       <c r="B124" t="str">
-        <v>猛士西安浐灞店</v>
+        <v>猛士西安经开店</v>
       </c>
       <c r="C124" t="str">
         <v>陕西省</v>
@@ -2515,7 +2515,7 @@
         <v>西安市</v>
       </c>
       <c r="E124" t="str">
-        <v>灞桥区</v>
+        <v>未央区</v>
       </c>
     </row>
     <row r="125">
@@ -2523,16 +2523,16 @@
         <v>西北区域</v>
       </c>
       <c r="B125" t="str">
-        <v>猛士西安未央店</v>
+        <v>猛士榆林草海则店</v>
       </c>
       <c r="C125" t="str">
         <v>陕西省</v>
       </c>
       <c r="D125" t="str">
-        <v>西安市</v>
+        <v>榆林市</v>
       </c>
       <c r="E125" t="str">
-        <v>未央区</v>
+        <v>横山区</v>
       </c>
     </row>
     <row r="126">
@@ -2540,16 +2540,16 @@
         <v>西北区域</v>
       </c>
       <c r="B126" t="str">
-        <v>猛士西安经开店</v>
+        <v>猛士乌鲁木齐店</v>
       </c>
       <c r="C126" t="str">
-        <v>陕西省</v>
+        <v>新疆维吾尔自治区</v>
       </c>
       <c r="D126" t="str">
-        <v>西安市</v>
+        <v>乌鲁木齐市</v>
       </c>
       <c r="E126" t="str">
-        <v>未央区</v>
+        <v>水磨沟区</v>
       </c>
     </row>
     <row r="127">
@@ -2557,50 +2557,50 @@
         <v>西北区域</v>
       </c>
       <c r="B127" t="str">
-        <v>猛士榆林草海则店</v>
+        <v>猛士乌鲁木齐喀什西路店</v>
       </c>
       <c r="C127" t="str">
-        <v>陕西省</v>
+        <v>新疆维吾尔自治区</v>
       </c>
       <c r="D127" t="str">
-        <v>榆林市</v>
+        <v>乌鲁木齐市</v>
       </c>
       <c r="E127" t="str">
-        <v>横山区</v>
+        <v>头屯河区</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>西北区域</v>
+        <v>东北区域</v>
       </c>
       <c r="B128" t="str">
-        <v>猛士乌鲁木齐店</v>
+        <v>猛士大庆让胡路区店</v>
       </c>
       <c r="C128" t="str">
-        <v>新疆维吾尔自治区</v>
+        <v>黑龙江省</v>
       </c>
       <c r="D128" t="str">
-        <v>乌鲁木齐市</v>
+        <v>大庆市</v>
       </c>
       <c r="E128" t="str">
-        <v>水磨沟区</v>
+        <v>让胡路区</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>西北区域</v>
+        <v>东北区域</v>
       </c>
       <c r="B129" t="str">
-        <v>猛士乌鲁木齐喀什西路店</v>
+        <v>猛士哈尔滨香坊店</v>
       </c>
       <c r="C129" t="str">
-        <v>新疆维吾尔自治区</v>
+        <v>黑龙江省</v>
       </c>
       <c r="D129" t="str">
-        <v>乌鲁木齐市</v>
+        <v>哈尔滨市</v>
       </c>
       <c r="E129" t="str">
-        <v>头屯河区</v>
+        <v>香坊区</v>
       </c>
     </row>
     <row r="130">
@@ -2608,16 +2608,16 @@
         <v>东北区域</v>
       </c>
       <c r="B130" t="str">
-        <v>猛士大庆让胡路授权服务中心</v>
+        <v>猛士北安店</v>
       </c>
       <c r="C130" t="str">
         <v>黑龙江省</v>
       </c>
       <c r="D130" t="str">
-        <v>大庆市</v>
+        <v>黑河市</v>
       </c>
       <c r="E130" t="str">
-        <v>让胡路区</v>
+        <v>北安市</v>
       </c>
     </row>
     <row r="131">
@@ -2625,16 +2625,16 @@
         <v>东北区域</v>
       </c>
       <c r="B131" t="str">
-        <v>猛士哈尔滨香坊店</v>
+        <v>猛士佳木斯郊区店</v>
       </c>
       <c r="C131" t="str">
         <v>黑龙江省</v>
       </c>
       <c r="D131" t="str">
-        <v>哈尔滨市</v>
+        <v>佳木斯市</v>
       </c>
       <c r="E131" t="str">
-        <v>香坊区</v>
+        <v>郊区</v>
       </c>
     </row>
     <row r="132">
@@ -2642,16 +2642,16 @@
         <v>东北区域</v>
       </c>
       <c r="B132" t="str">
-        <v>猛士北安授权服务中心</v>
+        <v>猛士牡丹江阳明区店</v>
       </c>
       <c r="C132" t="str">
         <v>黑龙江省</v>
       </c>
       <c r="D132" t="str">
-        <v>黑河市</v>
+        <v>牡丹江市</v>
       </c>
       <c r="E132" t="str">
-        <v>北安市</v>
+        <v>阳明区</v>
       </c>
     </row>
     <row r="133">
@@ -2659,16 +2659,16 @@
         <v>东北区域</v>
       </c>
       <c r="B133" t="str">
-        <v>猛士佳木斯授权服务中心</v>
+        <v>猛士齐齐哈尔铁锋区店</v>
       </c>
       <c r="C133" t="str">
         <v>黑龙江省</v>
       </c>
       <c r="D133" t="str">
-        <v>佳木斯市</v>
+        <v>齐齐哈尔市</v>
       </c>
       <c r="E133" t="str">
-        <v>郊区</v>
+        <v>铁锋区</v>
       </c>
     </row>
     <row r="134">
@@ -2676,16 +2676,16 @@
         <v>东北区域</v>
       </c>
       <c r="B134" t="str">
-        <v>猛士牡丹江授权服务中心</v>
+        <v>猛士松原宁江区店</v>
       </c>
       <c r="C134" t="str">
-        <v>黑龙江省</v>
+        <v>吉林省</v>
       </c>
       <c r="D134" t="str">
-        <v>牡丹江市</v>
+        <v>松原市</v>
       </c>
       <c r="E134" t="str">
-        <v>阳明区</v>
+        <v>宁江区</v>
       </c>
     </row>
     <row r="135">
@@ -2693,16 +2693,16 @@
         <v>东北区域</v>
       </c>
       <c r="B135" t="str">
-        <v>猛士齐齐哈尔铁锋授权服务中心</v>
+        <v>猛士长春经开店</v>
       </c>
       <c r="C135" t="str">
-        <v>黑龙江省</v>
+        <v>吉林省</v>
       </c>
       <c r="D135" t="str">
-        <v>齐齐哈尔市</v>
+        <v>长春市</v>
       </c>
       <c r="E135" t="str">
-        <v>铁锋区</v>
+        <v>二道区</v>
       </c>
     </row>
     <row r="136">
@@ -2710,16 +2710,16 @@
         <v>东北区域</v>
       </c>
       <c r="B136" t="str">
-        <v>猛士松原授权服务中心</v>
+        <v>猛士大连华北路店</v>
       </c>
       <c r="C136" t="str">
-        <v>吉林省</v>
+        <v>辽宁省</v>
       </c>
       <c r="D136" t="str">
-        <v>松原市</v>
+        <v>大连市</v>
       </c>
       <c r="E136" t="str">
-        <v>宁江区</v>
+        <v>甘井子区</v>
       </c>
     </row>
     <row r="137">
@@ -2727,16 +2727,16 @@
         <v>东北区域</v>
       </c>
       <c r="B137" t="str">
-        <v>猛士长春经开店</v>
+        <v>猛士沈阳店</v>
       </c>
       <c r="C137" t="str">
-        <v>吉林省</v>
+        <v>辽宁省</v>
       </c>
       <c r="D137" t="str">
-        <v>长春市</v>
+        <v>沈阳市</v>
       </c>
       <c r="E137" t="str">
-        <v>二道区</v>
+        <v>浑南区</v>
       </c>
     </row>
     <row r="138">
@@ -2744,16 +2744,16 @@
         <v>东北区域</v>
       </c>
       <c r="B138" t="str">
-        <v>猛士大连华北路店</v>
+        <v>猛士沈阳沈河店</v>
       </c>
       <c r="C138" t="str">
         <v>辽宁省</v>
       </c>
       <c r="D138" t="str">
-        <v>大连市</v>
+        <v>沈阳市</v>
       </c>
       <c r="E138" t="str">
-        <v>甘井子区</v>
+        <v>沈河区</v>
       </c>
     </row>
     <row r="139">
@@ -2761,16 +2761,16 @@
         <v>东北区域</v>
       </c>
       <c r="B139" t="str">
-        <v>猛士沈阳店</v>
+        <v>猛士包头九原店</v>
       </c>
       <c r="C139" t="str">
-        <v>辽宁省</v>
+        <v>内蒙古自治区</v>
       </c>
       <c r="D139" t="str">
-        <v>沈阳市</v>
+        <v>包头市</v>
       </c>
       <c r="E139" t="str">
-        <v>浑南区</v>
+        <v>九原区</v>
       </c>
     </row>
     <row r="140">
@@ -2778,16 +2778,16 @@
         <v>东北区域</v>
       </c>
       <c r="B140" t="str">
-        <v>猛士沈阳沈河店</v>
+        <v>猛士赤峰红山店</v>
       </c>
       <c r="C140" t="str">
-        <v>辽宁省</v>
+        <v>内蒙古自治区</v>
       </c>
       <c r="D140" t="str">
-        <v>沈阳市</v>
+        <v>赤峰市</v>
       </c>
       <c r="E140" t="str">
-        <v>沈河区</v>
+        <v>红山区</v>
       </c>
     </row>
     <row r="141">
@@ -2795,16 +2795,16 @@
         <v>东北区域</v>
       </c>
       <c r="B141" t="str">
-        <v>猛士包头九原店</v>
+        <v>猛士鄂尔多斯东胜店</v>
       </c>
       <c r="C141" t="str">
         <v>内蒙古自治区</v>
       </c>
       <c r="D141" t="str">
-        <v>包头市</v>
+        <v>鄂尔多斯市</v>
       </c>
       <c r="E141" t="str">
-        <v>九原区</v>
+        <v>东胜区</v>
       </c>
     </row>
     <row r="142">
@@ -2812,16 +2812,16 @@
         <v>东北区域</v>
       </c>
       <c r="B142" t="str">
-        <v>猛士赤峰红山店</v>
+        <v>猛士呼和浩特海西路店</v>
       </c>
       <c r="C142" t="str">
         <v>内蒙古自治区</v>
       </c>
       <c r="D142" t="str">
-        <v>赤峰市</v>
+        <v>呼和浩特市</v>
       </c>
       <c r="E142" t="str">
-        <v>红山区</v>
+        <v>回民区</v>
       </c>
     </row>
     <row r="143">
@@ -2829,16 +2829,16 @@
         <v>东北区域</v>
       </c>
       <c r="B143" t="str">
-        <v>猛士鄂尔多斯东胜店</v>
+        <v>猛士呼伦贝尔汽车城店</v>
       </c>
       <c r="C143" t="str">
         <v>内蒙古自治区</v>
       </c>
       <c r="D143" t="str">
-        <v>鄂尔多斯市</v>
+        <v>呼伦贝尔市</v>
       </c>
       <c r="E143" t="str">
-        <v>东胜区</v>
+        <v>鄂温克族自治旗</v>
       </c>
     </row>
     <row r="144">
@@ -2846,16 +2846,16 @@
         <v>东北区域</v>
       </c>
       <c r="B144" t="str">
-        <v>猛士呼和浩特海西路店</v>
+        <v>猛士通辽万林店</v>
       </c>
       <c r="C144" t="str">
         <v>内蒙古自治区</v>
       </c>
       <c r="D144" t="str">
-        <v>呼和浩特市</v>
+        <v>通辽市</v>
       </c>
       <c r="E144" t="str">
-        <v>回民区</v>
+        <v>科尔沁区</v>
       </c>
     </row>
     <row r="145">
@@ -2863,16 +2863,16 @@
         <v>东北区域</v>
       </c>
       <c r="B145" t="str">
-        <v>猛士呼伦贝尔汽车城店</v>
+        <v>猛士大同经开店</v>
       </c>
       <c r="C145" t="str">
-        <v>内蒙古自治区</v>
+        <v>山西省</v>
       </c>
       <c r="D145" t="str">
-        <v>呼伦贝尔市</v>
+        <v>大同市</v>
       </c>
       <c r="E145" t="str">
-        <v>鄂温克族自治旗</v>
+        <v>云州区</v>
       </c>
     </row>
     <row r="146">
@@ -2880,16 +2880,16 @@
         <v>东北区域</v>
       </c>
       <c r="B146" t="str">
-        <v>猛士通辽万林店</v>
+        <v>猛士晋城路宝店</v>
       </c>
       <c r="C146" t="str">
-        <v>内蒙古自治区</v>
+        <v>山西省</v>
       </c>
       <c r="D146" t="str">
-        <v>通辽市</v>
+        <v>晋城市</v>
       </c>
       <c r="E146" t="str">
-        <v>科尔沁区</v>
+        <v>泽州县</v>
       </c>
     </row>
     <row r="147">
@@ -2897,16 +2897,16 @@
         <v>东北区域</v>
       </c>
       <c r="B147" t="str">
-        <v>猛士大同经开店</v>
+        <v>猛士太原龙城店</v>
       </c>
       <c r="C147" t="str">
         <v>山西省</v>
       </c>
       <c r="D147" t="str">
-        <v>大同市</v>
+        <v>太原市</v>
       </c>
       <c r="E147" t="str">
-        <v>云州区</v>
+        <v>小店区</v>
       </c>
     </row>
     <row r="148">
@@ -2914,55 +2914,21 @@
         <v>东北区域</v>
       </c>
       <c r="B148" t="str">
-        <v>猛士晋城路宝店</v>
+        <v>猛士长治潞州店</v>
       </c>
       <c r="C148" t="str">
         <v>山西省</v>
       </c>
       <c r="D148" t="str">
-        <v>晋城市</v>
+        <v>长治市</v>
       </c>
       <c r="E148" t="str">
-        <v>泽州县</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="str">
-        <v>东北区域</v>
-      </c>
-      <c r="B149" t="str">
-        <v>猛士太原龙城店</v>
-      </c>
-      <c r="C149" t="str">
-        <v>山西省</v>
-      </c>
-      <c r="D149" t="str">
-        <v>太原市</v>
-      </c>
-      <c r="E149" t="str">
-        <v>小店区</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="str">
-        <v>东北区域</v>
-      </c>
-      <c r="B150" t="str">
-        <v>猛士长治潞州店</v>
-      </c>
-      <c r="C150" t="str">
-        <v>山西省</v>
-      </c>
-      <c r="D150" t="str">
-        <v>长治市</v>
-      </c>
-      <c r="E150" t="str">
         <v>潞州区</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E150"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E148"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/售后网络.xlsx
+++ b/docs/售后网络.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E148"/>
+  <dimension ref="A1:E147"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -1010,16 +1010,16 @@
         <v>华北区域</v>
       </c>
       <c r="B36" t="str">
-        <v>猛士聊城东昌府店</v>
+        <v>猛士临沂河东店</v>
       </c>
       <c r="C36" t="str">
         <v>山东省</v>
       </c>
       <c r="D36" t="str">
-        <v>聊城市</v>
+        <v>临沂市</v>
       </c>
       <c r="E36" t="str">
-        <v>东昌府区</v>
+        <v>河东区</v>
       </c>
     </row>
     <row r="37">
@@ -1027,16 +1027,16 @@
         <v>华北区域</v>
       </c>
       <c r="B37" t="str">
-        <v>猛士临沂河东店</v>
+        <v>猛士青岛市北店</v>
       </c>
       <c r="C37" t="str">
         <v>山东省</v>
       </c>
       <c r="D37" t="str">
-        <v>临沂市</v>
+        <v>青岛市</v>
       </c>
       <c r="E37" t="str">
-        <v>河东区</v>
+        <v>市北区</v>
       </c>
     </row>
     <row r="38">
@@ -1044,7 +1044,7 @@
         <v>华北区域</v>
       </c>
       <c r="B38" t="str">
-        <v>猛士青岛市北店</v>
+        <v>猛士青岛长沙路店</v>
       </c>
       <c r="C38" t="str">
         <v>山东省</v>
@@ -1061,16 +1061,16 @@
         <v>华北区域</v>
       </c>
       <c r="B39" t="str">
-        <v>猛士青岛长沙路店</v>
+        <v>猛士威海经区店</v>
       </c>
       <c r="C39" t="str">
         <v>山东省</v>
       </c>
       <c r="D39" t="str">
-        <v>青岛市</v>
+        <v>威海市</v>
       </c>
       <c r="E39" t="str">
-        <v>市北区</v>
+        <v>环翠区</v>
       </c>
     </row>
     <row r="40">
@@ -1078,16 +1078,16 @@
         <v>华北区域</v>
       </c>
       <c r="B40" t="str">
-        <v>猛士威海经区店</v>
+        <v>猛士潍坊奎文店</v>
       </c>
       <c r="C40" t="str">
         <v>山东省</v>
       </c>
       <c r="D40" t="str">
-        <v>威海市</v>
+        <v>潍坊市</v>
       </c>
       <c r="E40" t="str">
-        <v>环翠区</v>
+        <v>奎文区</v>
       </c>
     </row>
     <row r="41">
@@ -1095,16 +1095,16 @@
         <v>华北区域</v>
       </c>
       <c r="B41" t="str">
-        <v>猛士潍坊奎文店</v>
+        <v>猛士烟台机场路店</v>
       </c>
       <c r="C41" t="str">
         <v>山东省</v>
       </c>
       <c r="D41" t="str">
-        <v>潍坊市</v>
+        <v>烟台市</v>
       </c>
       <c r="E41" t="str">
-        <v>奎文区</v>
+        <v>芝罘区</v>
       </c>
     </row>
     <row r="42">
@@ -1112,16 +1112,16 @@
         <v>华北区域</v>
       </c>
       <c r="B42" t="str">
-        <v>猛士烟台机场路店</v>
+        <v>猛士淄博经开店</v>
       </c>
       <c r="C42" t="str">
         <v>山东省</v>
       </c>
       <c r="D42" t="str">
-        <v>烟台市</v>
+        <v>淄博市</v>
       </c>
       <c r="E42" t="str">
-        <v>芝罘区</v>
+        <v>张店区</v>
       </c>
     </row>
     <row r="43">
@@ -1129,33 +1129,33 @@
         <v>华北区域</v>
       </c>
       <c r="B43" t="str">
-        <v>猛士淄博经开店</v>
+        <v>猛士天津北辰店</v>
       </c>
       <c r="C43" t="str">
-        <v>山东省</v>
+        <v>天津市</v>
       </c>
       <c r="D43" t="str">
-        <v>淄博市</v>
+        <v>天津市</v>
       </c>
       <c r="E43" t="str">
-        <v>张店区</v>
+        <v>北辰区</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>华北区域</v>
+        <v>华中区域</v>
       </c>
       <c r="B44" t="str">
-        <v>猛士天津北辰店</v>
+        <v>猛士安庆宜秀店</v>
       </c>
       <c r="C44" t="str">
-        <v>天津市</v>
+        <v>安徽省</v>
       </c>
       <c r="D44" t="str">
-        <v>天津市</v>
+        <v>安庆市</v>
       </c>
       <c r="E44" t="str">
-        <v>北辰区</v>
+        <v>宜秀区</v>
       </c>
     </row>
     <row r="45">
@@ -1163,16 +1163,16 @@
         <v>华中区域</v>
       </c>
       <c r="B45" t="str">
-        <v>猛士安庆宜秀店</v>
+        <v>猛士阜阳颍州店</v>
       </c>
       <c r="C45" t="str">
         <v>安徽省</v>
       </c>
       <c r="D45" t="str">
-        <v>安庆市</v>
+        <v>阜阳市</v>
       </c>
       <c r="E45" t="str">
-        <v>宜秀区</v>
+        <v>颍州区</v>
       </c>
     </row>
     <row r="46">
@@ -1180,16 +1180,16 @@
         <v>华中区域</v>
       </c>
       <c r="B46" t="str">
-        <v>猛士阜阳颍州店</v>
+        <v>猛士合肥庐阳店</v>
       </c>
       <c r="C46" t="str">
         <v>安徽省</v>
       </c>
       <c r="D46" t="str">
-        <v>阜阳市</v>
+        <v>合肥市</v>
       </c>
       <c r="E46" t="str">
-        <v>颍州区</v>
+        <v>庐阳区</v>
       </c>
     </row>
     <row r="47">
@@ -1197,16 +1197,16 @@
         <v>华中区域</v>
       </c>
       <c r="B47" t="str">
-        <v>猛士合肥庐阳店</v>
+        <v>猛士六安金安店</v>
       </c>
       <c r="C47" t="str">
         <v>安徽省</v>
       </c>
       <c r="D47" t="str">
-        <v>合肥市</v>
+        <v>六安市</v>
       </c>
       <c r="E47" t="str">
-        <v>庐阳区</v>
+        <v>金安区</v>
       </c>
     </row>
     <row r="48">
@@ -1214,16 +1214,16 @@
         <v>华中区域</v>
       </c>
       <c r="B48" t="str">
-        <v>猛士六安金安店</v>
+        <v>猛士安阳安阳县店</v>
       </c>
       <c r="C48" t="str">
-        <v>安徽省</v>
+        <v>河南省</v>
       </c>
       <c r="D48" t="str">
-        <v>六安市</v>
+        <v>安阳市</v>
       </c>
       <c r="E48" t="str">
-        <v>金安区</v>
+        <v>安阳县</v>
       </c>
     </row>
     <row r="49">
@@ -1231,16 +1231,16 @@
         <v>华中区域</v>
       </c>
       <c r="B49" t="str">
-        <v>猛士安阳安阳县店</v>
+        <v>猛士鹤壁淇滨区店</v>
       </c>
       <c r="C49" t="str">
         <v>河南省</v>
       </c>
       <c r="D49" t="str">
-        <v>安阳市</v>
+        <v>鹤壁市</v>
       </c>
       <c r="E49" t="str">
-        <v>安阳县</v>
+        <v>淇滨区</v>
       </c>
     </row>
     <row r="50">
@@ -1248,16 +1248,16 @@
         <v>华中区域</v>
       </c>
       <c r="B50" t="str">
-        <v>猛士鹤壁淇滨区店</v>
+        <v>猛士开封龙亭区店</v>
       </c>
       <c r="C50" t="str">
         <v>河南省</v>
       </c>
       <c r="D50" t="str">
-        <v>鹤壁市</v>
+        <v>开封市</v>
       </c>
       <c r="E50" t="str">
-        <v>淇滨区</v>
+        <v>龙亭区</v>
       </c>
     </row>
     <row r="51">
@@ -1265,16 +1265,16 @@
         <v>华中区域</v>
       </c>
       <c r="B51" t="str">
-        <v>猛士开封龙亭区店</v>
+        <v>猛士洛阳威佳国润店</v>
       </c>
       <c r="C51" t="str">
         <v>河南省</v>
       </c>
       <c r="D51" t="str">
-        <v>开封市</v>
+        <v>洛阳市</v>
       </c>
       <c r="E51" t="str">
-        <v>龙亭区</v>
+        <v>瀍河回族区</v>
       </c>
     </row>
     <row r="52">
@@ -1282,16 +1282,16 @@
         <v>华中区域</v>
       </c>
       <c r="B52" t="str">
-        <v>猛士洛阳威佳国润店</v>
+        <v>猛士漯河源汇区店</v>
       </c>
       <c r="C52" t="str">
         <v>河南省</v>
       </c>
       <c r="D52" t="str">
-        <v>洛阳市</v>
+        <v>漯河市</v>
       </c>
       <c r="E52" t="str">
-        <v>瀍河回族区</v>
+        <v>源汇区</v>
       </c>
     </row>
     <row r="53">
@@ -1299,16 +1299,16 @@
         <v>华中区域</v>
       </c>
       <c r="B53" t="str">
-        <v>猛士漯河源汇区店</v>
+        <v>猛士平顶山卫东区店</v>
       </c>
       <c r="C53" t="str">
         <v>河南省</v>
       </c>
       <c r="D53" t="str">
-        <v>漯河市</v>
+        <v>平顶山市</v>
       </c>
       <c r="E53" t="str">
-        <v>源汇区</v>
+        <v>卫东区</v>
       </c>
     </row>
     <row r="54">
@@ -1316,16 +1316,16 @@
         <v>华中区域</v>
       </c>
       <c r="B54" t="str">
-        <v>猛士平顶山卫东区店</v>
+        <v>猛士濮阳华龙区店</v>
       </c>
       <c r="C54" t="str">
         <v>河南省</v>
       </c>
       <c r="D54" t="str">
-        <v>平顶山市</v>
+        <v>濮阳市</v>
       </c>
       <c r="E54" t="str">
-        <v>卫东区</v>
+        <v>华龙区</v>
       </c>
     </row>
     <row r="55">
@@ -1333,16 +1333,16 @@
         <v>华中区域</v>
       </c>
       <c r="B55" t="str">
-        <v>猛士濮阳华龙区店</v>
+        <v>猛士商丘梁园区店</v>
       </c>
       <c r="C55" t="str">
         <v>河南省</v>
       </c>
       <c r="D55" t="str">
-        <v>濮阳市</v>
+        <v>商丘市</v>
       </c>
       <c r="E55" t="str">
-        <v>华龙区</v>
+        <v>梁园区</v>
       </c>
     </row>
     <row r="56">
@@ -1350,16 +1350,16 @@
         <v>华中区域</v>
       </c>
       <c r="B56" t="str">
-        <v>猛士商丘梁园区店</v>
+        <v>猛士新乡店</v>
       </c>
       <c r="C56" t="str">
         <v>河南省</v>
       </c>
       <c r="D56" t="str">
-        <v>商丘市</v>
+        <v>新乡市</v>
       </c>
       <c r="E56" t="str">
-        <v>梁园区</v>
+        <v>新乡县</v>
       </c>
     </row>
     <row r="57">
@@ -1367,16 +1367,16 @@
         <v>华中区域</v>
       </c>
       <c r="B57" t="str">
-        <v>猛士新乡店</v>
+        <v>猛士许昌魏都区店</v>
       </c>
       <c r="C57" t="str">
         <v>河南省</v>
       </c>
       <c r="D57" t="str">
-        <v>新乡市</v>
+        <v>许昌市</v>
       </c>
       <c r="E57" t="str">
-        <v>新乡县</v>
+        <v>魏都区</v>
       </c>
     </row>
     <row r="58">
@@ -1384,16 +1384,16 @@
         <v>华中区域</v>
       </c>
       <c r="B58" t="str">
-        <v>猛士许昌魏都区店</v>
+        <v>猛士郑州经开店</v>
       </c>
       <c r="C58" t="str">
         <v>河南省</v>
       </c>
       <c r="D58" t="str">
-        <v>许昌市</v>
+        <v>郑州市</v>
       </c>
       <c r="E58" t="str">
-        <v>魏都区</v>
+        <v>管城回族区</v>
       </c>
     </row>
     <row r="59">
@@ -1401,7 +1401,7 @@
         <v>华中区域</v>
       </c>
       <c r="B59" t="str">
-        <v>猛士郑州经开店</v>
+        <v>猛士郑州郑东店</v>
       </c>
       <c r="C59" t="str">
         <v>河南省</v>
@@ -1418,7 +1418,7 @@
         <v>华中区域</v>
       </c>
       <c r="B60" t="str">
-        <v>猛士郑州郑东店</v>
+        <v>猛士郑州北汽贸店</v>
       </c>
       <c r="C60" t="str">
         <v>河南省</v>
@@ -1427,7 +1427,7 @@
         <v>郑州市</v>
       </c>
       <c r="E60" t="str">
-        <v>管城回族区</v>
+        <v>惠济区</v>
       </c>
     </row>
     <row r="61">
@@ -1435,16 +1435,16 @@
         <v>华中区域</v>
       </c>
       <c r="B61" t="str">
-        <v>猛士郑州北汽贸店</v>
+        <v>猛士驻马店上蔡县店</v>
       </c>
       <c r="C61" t="str">
         <v>河南省</v>
       </c>
       <c r="D61" t="str">
-        <v>郑州市</v>
+        <v>驻马店市</v>
       </c>
       <c r="E61" t="str">
-        <v>惠济区</v>
+        <v>上蔡县</v>
       </c>
     </row>
     <row r="62">
@@ -1452,16 +1452,16 @@
         <v>华中区域</v>
       </c>
       <c r="B62" t="str">
-        <v>猛士驻马店上蔡县店</v>
+        <v>猛士恩施店</v>
       </c>
       <c r="C62" t="str">
-        <v>河南省</v>
+        <v>湖北省</v>
       </c>
       <c r="D62" t="str">
-        <v>驻马店市</v>
+        <v>恩施土家族苗族自治州</v>
       </c>
       <c r="E62" t="str">
-        <v>上蔡县</v>
+        <v>恩施市</v>
       </c>
     </row>
     <row r="63">
@@ -1469,16 +1469,16 @@
         <v>华中区域</v>
       </c>
       <c r="B63" t="str">
-        <v>猛士恩施店</v>
+        <v>猛士十堰张湾店</v>
       </c>
       <c r="C63" t="str">
         <v>湖北省</v>
       </c>
       <c r="D63" t="str">
-        <v>恩施土家族苗族自治州</v>
+        <v>十堰市</v>
       </c>
       <c r="E63" t="str">
-        <v>恩施市</v>
+        <v>张湾区</v>
       </c>
     </row>
     <row r="64">
@@ -1486,16 +1486,16 @@
         <v>华中区域</v>
       </c>
       <c r="B64" t="str">
-        <v>猛士十堰张湾店</v>
+        <v>猛士武汉汉阳区店</v>
       </c>
       <c r="C64" t="str">
         <v>湖北省</v>
       </c>
       <c r="D64" t="str">
-        <v>十堰市</v>
+        <v>武汉市</v>
       </c>
       <c r="E64" t="str">
-        <v>张湾区</v>
+        <v>汉阳区</v>
       </c>
     </row>
     <row r="65">
@@ -1503,7 +1503,7 @@
         <v>华中区域</v>
       </c>
       <c r="B65" t="str">
-        <v>猛士武汉汉阳区店</v>
+        <v>猛士武汉光谷店</v>
       </c>
       <c r="C65" t="str">
         <v>湖北省</v>
@@ -1512,7 +1512,7 @@
         <v>武汉市</v>
       </c>
       <c r="E65" t="str">
-        <v>汉阳区</v>
+        <v>江夏区</v>
       </c>
     </row>
     <row r="66">
@@ -1520,7 +1520,7 @@
         <v>华中区域</v>
       </c>
       <c r="B66" t="str">
-        <v>猛士武汉光谷店</v>
+        <v>猛士汽车001武汉旗舰店</v>
       </c>
       <c r="C66" t="str">
         <v>湖北省</v>
@@ -1529,7 +1529,7 @@
         <v>武汉市</v>
       </c>
       <c r="E66" t="str">
-        <v>江夏区</v>
+        <v>江岸区</v>
       </c>
     </row>
     <row r="67">
@@ -1537,16 +1537,16 @@
         <v>华中区域</v>
       </c>
       <c r="B67" t="str">
-        <v>猛士汽车001武汉旗舰店</v>
+        <v>猛士襄阳襄州店</v>
       </c>
       <c r="C67" t="str">
         <v>湖北省</v>
       </c>
       <c r="D67" t="str">
-        <v>武汉市</v>
+        <v>襄阳市</v>
       </c>
       <c r="E67" t="str">
-        <v>江岸区</v>
+        <v>襄州区</v>
       </c>
     </row>
     <row r="68">
@@ -1554,16 +1554,16 @@
         <v>华中区域</v>
       </c>
       <c r="B68" t="str">
-        <v>猛士襄阳襄州店</v>
+        <v>猛士孝感孝南区店</v>
       </c>
       <c r="C68" t="str">
         <v>湖北省</v>
       </c>
       <c r="D68" t="str">
-        <v>襄阳市</v>
+        <v>孝感市</v>
       </c>
       <c r="E68" t="str">
-        <v>襄州区</v>
+        <v>孝南区</v>
       </c>
     </row>
     <row r="69">
@@ -1571,16 +1571,16 @@
         <v>华中区域</v>
       </c>
       <c r="B69" t="str">
-        <v>猛士孝感孝南区店</v>
+        <v>猛士宜昌伍家岗店</v>
       </c>
       <c r="C69" t="str">
         <v>湖北省</v>
       </c>
       <c r="D69" t="str">
-        <v>孝感市</v>
+        <v>宜昌市</v>
       </c>
       <c r="E69" t="str">
-        <v>孝南区</v>
+        <v>伍家岗区</v>
       </c>
     </row>
     <row r="70">
@@ -1588,16 +1588,16 @@
         <v>华中区域</v>
       </c>
       <c r="B70" t="str">
-        <v>猛士宜昌伍家岗店</v>
+        <v>猛士衡阳蒸湘区店</v>
       </c>
       <c r="C70" t="str">
-        <v>湖北省</v>
+        <v>湖南省</v>
       </c>
       <c r="D70" t="str">
-        <v>宜昌市</v>
+        <v>衡阳市</v>
       </c>
       <c r="E70" t="str">
-        <v>伍家岗区</v>
+        <v>蒸湘区</v>
       </c>
     </row>
     <row r="71">
@@ -1605,16 +1605,16 @@
         <v>华中区域</v>
       </c>
       <c r="B71" t="str">
-        <v>猛士衡阳蒸湘区店</v>
+        <v>猛士怀化鹤城店</v>
       </c>
       <c r="C71" t="str">
         <v>湖南省</v>
       </c>
       <c r="D71" t="str">
-        <v>衡阳市</v>
+        <v>怀化市</v>
       </c>
       <c r="E71" t="str">
-        <v>蒸湘区</v>
+        <v>鹤城区</v>
       </c>
     </row>
     <row r="72">
@@ -1622,16 +1622,16 @@
         <v>华中区域</v>
       </c>
       <c r="B72" t="str">
-        <v>猛士怀化鹤城店</v>
+        <v>猛士长沙开福店</v>
       </c>
       <c r="C72" t="str">
         <v>湖南省</v>
       </c>
       <c r="D72" t="str">
-        <v>怀化市</v>
+        <v>长沙市</v>
       </c>
       <c r="E72" t="str">
-        <v>鹤城区</v>
+        <v>开福区</v>
       </c>
     </row>
     <row r="73">
@@ -1639,7 +1639,7 @@
         <v>华中区域</v>
       </c>
       <c r="B73" t="str">
-        <v>猛士长沙开福店</v>
+        <v>猛士长沙中南店</v>
       </c>
       <c r="C73" t="str">
         <v>湖南省</v>
@@ -1648,7 +1648,7 @@
         <v>长沙市</v>
       </c>
       <c r="E73" t="str">
-        <v>开福区</v>
+        <v>长沙县</v>
       </c>
     </row>
     <row r="74">
@@ -1656,16 +1656,16 @@
         <v>华中区域</v>
       </c>
       <c r="B74" t="str">
-        <v>猛士长沙中南店</v>
+        <v>猛士南昌青山湖区店</v>
       </c>
       <c r="C74" t="str">
-        <v>湖南省</v>
+        <v>江西省</v>
       </c>
       <c r="D74" t="str">
-        <v>长沙市</v>
+        <v>南昌市</v>
       </c>
       <c r="E74" t="str">
-        <v>长沙县</v>
+        <v>青山湖区</v>
       </c>
     </row>
     <row r="75">
@@ -1673,33 +1673,33 @@
         <v>华中区域</v>
       </c>
       <c r="B75" t="str">
-        <v>猛士南昌青山湖区店</v>
+        <v>猛士上饶月亮湾店</v>
       </c>
       <c r="C75" t="str">
         <v>江西省</v>
       </c>
       <c r="D75" t="str">
-        <v>南昌市</v>
+        <v>上饶市</v>
       </c>
       <c r="E75" t="str">
-        <v>青山湖区</v>
+        <v>广信区</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>华中区域</v>
+        <v>华南区域</v>
       </c>
       <c r="B76" t="str">
-        <v>猛士上饶月亮湾店</v>
+        <v>猛士福州仓山店</v>
       </c>
       <c r="C76" t="str">
-        <v>江西省</v>
+        <v>福建省</v>
       </c>
       <c r="D76" t="str">
-        <v>上饶市</v>
+        <v>福州市</v>
       </c>
       <c r="E76" t="str">
-        <v>广信区</v>
+        <v>仓山区</v>
       </c>
     </row>
     <row r="77">
@@ -1707,16 +1707,16 @@
         <v>华南区域</v>
       </c>
       <c r="B77" t="str">
-        <v>猛士福州仓山店</v>
+        <v>猛士宁德蕉城区店</v>
       </c>
       <c r="C77" t="str">
         <v>福建省</v>
       </c>
       <c r="D77" t="str">
-        <v>福州市</v>
+        <v>宁德市</v>
       </c>
       <c r="E77" t="str">
-        <v>仓山区</v>
+        <v>蕉城区</v>
       </c>
     </row>
     <row r="78">
@@ -1724,16 +1724,16 @@
         <v>华南区域</v>
       </c>
       <c r="B78" t="str">
-        <v>猛士宁德蕉城区店</v>
+        <v>猛士泉州鲤城店</v>
       </c>
       <c r="C78" t="str">
         <v>福建省</v>
       </c>
       <c r="D78" t="str">
-        <v>宁德市</v>
+        <v>泉州市</v>
       </c>
       <c r="E78" t="str">
-        <v>蕉城区</v>
+        <v>鲤城区</v>
       </c>
     </row>
     <row r="79">
@@ -1741,16 +1741,16 @@
         <v>华南区域</v>
       </c>
       <c r="B79" t="str">
-        <v>猛士泉州鲤城店</v>
+        <v>猛士厦门翔安店</v>
       </c>
       <c r="C79" t="str">
         <v>福建省</v>
       </c>
       <c r="D79" t="str">
-        <v>泉州市</v>
+        <v>厦门市</v>
       </c>
       <c r="E79" t="str">
-        <v>鲤城区</v>
+        <v>翔安区</v>
       </c>
     </row>
     <row r="80">
@@ -1758,16 +1758,16 @@
         <v>华南区域</v>
       </c>
       <c r="B80" t="str">
-        <v>猛士厦门翔安店</v>
+        <v>猛士东莞塘厦店</v>
       </c>
       <c r="C80" t="str">
-        <v>福建省</v>
+        <v>广东省</v>
       </c>
       <c r="D80" t="str">
-        <v>厦门市</v>
+        <v>东莞市</v>
       </c>
       <c r="E80" t="str">
-        <v>翔安区</v>
+        <v>塘厦镇</v>
       </c>
     </row>
     <row r="81">
@@ -1775,16 +1775,16 @@
         <v>华南区域</v>
       </c>
       <c r="B81" t="str">
-        <v>猛士东莞塘厦店</v>
+        <v>猛士佛山禅城店</v>
       </c>
       <c r="C81" t="str">
         <v>广东省</v>
       </c>
       <c r="D81" t="str">
-        <v>东莞市</v>
+        <v>佛山市</v>
       </c>
       <c r="E81" t="str">
-        <v>塘厦镇</v>
+        <v>禅城区</v>
       </c>
     </row>
     <row r="82">
@@ -1792,7 +1792,7 @@
         <v>华南区域</v>
       </c>
       <c r="B82" t="str">
-        <v>猛士佛山禅城店</v>
+        <v>猛士佛山海八路店</v>
       </c>
       <c r="C82" t="str">
         <v>广东省</v>
@@ -1801,7 +1801,7 @@
         <v>佛山市</v>
       </c>
       <c r="E82" t="str">
-        <v>禅城区</v>
+        <v>南海区</v>
       </c>
     </row>
     <row r="83">
@@ -1809,16 +1809,16 @@
         <v>华南区域</v>
       </c>
       <c r="B83" t="str">
-        <v>猛士佛山海八路店</v>
+        <v>猛士广州番禺店</v>
       </c>
       <c r="C83" t="str">
         <v>广东省</v>
       </c>
       <c r="D83" t="str">
-        <v>佛山市</v>
+        <v>广州市</v>
       </c>
       <c r="E83" t="str">
-        <v>南海区</v>
+        <v>番禺区</v>
       </c>
     </row>
     <row r="84">
@@ -1826,7 +1826,7 @@
         <v>华南区域</v>
       </c>
       <c r="B84" t="str">
-        <v>猛士广州番禺店</v>
+        <v>猛士广州龙洞店</v>
       </c>
       <c r="C84" t="str">
         <v>广东省</v>
@@ -1835,7 +1835,7 @@
         <v>广州市</v>
       </c>
       <c r="E84" t="str">
-        <v>番禺区</v>
+        <v>天河区</v>
       </c>
     </row>
     <row r="85">
@@ -1843,16 +1843,16 @@
         <v>华南区域</v>
       </c>
       <c r="B85" t="str">
-        <v>猛士广州龙洞店</v>
+        <v>猛士惠州惠城店</v>
       </c>
       <c r="C85" t="str">
         <v>广东省</v>
       </c>
       <c r="D85" t="str">
-        <v>广州市</v>
+        <v>惠州市</v>
       </c>
       <c r="E85" t="str">
-        <v>天河区</v>
+        <v>惠城区</v>
       </c>
     </row>
     <row r="86">
@@ -1860,16 +1860,16 @@
         <v>华南区域</v>
       </c>
       <c r="B86" t="str">
-        <v>猛士惠州惠城店</v>
+        <v>猛士梅州梅江店</v>
       </c>
       <c r="C86" t="str">
         <v>广东省</v>
       </c>
       <c r="D86" t="str">
-        <v>惠州市</v>
+        <v>梅州市</v>
       </c>
       <c r="E86" t="str">
-        <v>惠城区</v>
+        <v>梅江区</v>
       </c>
     </row>
     <row r="87">
@@ -1877,16 +1877,16 @@
         <v>华南区域</v>
       </c>
       <c r="B87" t="str">
-        <v>猛士梅州梅江店</v>
+        <v>猛士汕头高新店</v>
       </c>
       <c r="C87" t="str">
         <v>广东省</v>
       </c>
       <c r="D87" t="str">
-        <v>梅州市</v>
+        <v>汕头市</v>
       </c>
       <c r="E87" t="str">
-        <v>梅江区</v>
+        <v>金平区</v>
       </c>
     </row>
     <row r="88">
@@ -1894,16 +1894,16 @@
         <v>华南区域</v>
       </c>
       <c r="B88" t="str">
-        <v>猛士汕头高新店</v>
+        <v>猛士深圳宝安店</v>
       </c>
       <c r="C88" t="str">
         <v>广东省</v>
       </c>
       <c r="D88" t="str">
-        <v>汕头市</v>
+        <v>深圳市</v>
       </c>
       <c r="E88" t="str">
-        <v>金平区</v>
+        <v>宝安区</v>
       </c>
     </row>
     <row r="89">
@@ -1911,16 +1911,16 @@
         <v>华南区域</v>
       </c>
       <c r="B89" t="str">
-        <v>猛士深圳宝安店</v>
+        <v>猛士湛江赤坎区店</v>
       </c>
       <c r="C89" t="str">
         <v>广东省</v>
       </c>
       <c r="D89" t="str">
-        <v>深圳市</v>
+        <v>湛江市</v>
       </c>
       <c r="E89" t="str">
-        <v>宝安区</v>
+        <v>赤坎区</v>
       </c>
     </row>
     <row r="90">
@@ -1928,16 +1928,16 @@
         <v>华南区域</v>
       </c>
       <c r="B90" t="str">
-        <v>猛士湛江赤坎区店</v>
+        <v>猛士中山小榄店</v>
       </c>
       <c r="C90" t="str">
         <v>广东省</v>
       </c>
       <c r="D90" t="str">
-        <v>湛江市</v>
+        <v>中山市</v>
       </c>
       <c r="E90" t="str">
-        <v>赤坎区</v>
+        <v>小榄镇</v>
       </c>
     </row>
     <row r="91">
@@ -1945,16 +1945,16 @@
         <v>华南区域</v>
       </c>
       <c r="B91" t="str">
-        <v>猛士中山小榄店</v>
+        <v>猛士南宁江南店</v>
       </c>
       <c r="C91" t="str">
-        <v>广东省</v>
+        <v>广西壮族自治区</v>
       </c>
       <c r="D91" t="str">
-        <v>中山市</v>
+        <v>南宁市</v>
       </c>
       <c r="E91" t="str">
-        <v>小榄镇</v>
+        <v>江南区</v>
       </c>
     </row>
     <row r="92">
@@ -1962,16 +1962,16 @@
         <v>华南区域</v>
       </c>
       <c r="B92" t="str">
-        <v>猛士南宁江南店</v>
+        <v>猛士海口美兰店</v>
       </c>
       <c r="C92" t="str">
-        <v>广西壮族自治区</v>
+        <v>海南省</v>
       </c>
       <c r="D92" t="str">
-        <v>南宁市</v>
+        <v>海口市</v>
       </c>
       <c r="E92" t="str">
-        <v>江南区</v>
+        <v>美兰区</v>
       </c>
     </row>
     <row r="93">
@@ -1979,33 +1979,33 @@
         <v>华南区域</v>
       </c>
       <c r="B93" t="str">
-        <v>猛士海口美兰店</v>
+        <v>猛士三亚吉阳区店</v>
       </c>
       <c r="C93" t="str">
         <v>海南省</v>
       </c>
       <c r="D93" t="str">
-        <v>海口市</v>
+        <v>三亚市</v>
       </c>
       <c r="E93" t="str">
-        <v>美兰区</v>
+        <v>吉阳区</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>华南区域</v>
+        <v>西南区域</v>
       </c>
       <c r="B94" t="str">
-        <v>猛士三亚吉阳区店</v>
+        <v>猛士重庆九龙坡店</v>
       </c>
       <c r="C94" t="str">
-        <v>海南省</v>
+        <v>重庆市</v>
       </c>
       <c r="D94" t="str">
-        <v>三亚市</v>
+        <v>重庆市</v>
       </c>
       <c r="E94" t="str">
-        <v>吉阳区</v>
+        <v>九龙坡区</v>
       </c>
     </row>
     <row r="95">
@@ -2013,7 +2013,7 @@
         <v>西南区域</v>
       </c>
       <c r="B95" t="str">
-        <v>猛士重庆九龙坡店</v>
+        <v>猛士重庆海峡路店</v>
       </c>
       <c r="C95" t="str">
         <v>重庆市</v>
@@ -2022,7 +2022,7 @@
         <v>重庆市</v>
       </c>
       <c r="E95" t="str">
-        <v>九龙坡区</v>
+        <v>南岸区</v>
       </c>
     </row>
     <row r="96">
@@ -2030,7 +2030,7 @@
         <v>西南区域</v>
       </c>
       <c r="B96" t="str">
-        <v>猛士重庆海峡路店</v>
+        <v>猛士重庆渝北店</v>
       </c>
       <c r="C96" t="str">
         <v>重庆市</v>
@@ -2039,7 +2039,7 @@
         <v>重庆市</v>
       </c>
       <c r="E96" t="str">
-        <v>南岸区</v>
+        <v>渝北区</v>
       </c>
     </row>
     <row r="97">
@@ -2047,16 +2047,16 @@
         <v>西南区域</v>
       </c>
       <c r="B97" t="str">
-        <v>猛士重庆渝北店</v>
+        <v>猛士贵阳观山湖店</v>
       </c>
       <c r="C97" t="str">
-        <v>重庆市</v>
+        <v>贵州省</v>
       </c>
       <c r="D97" t="str">
-        <v>重庆市</v>
+        <v>贵阳市</v>
       </c>
       <c r="E97" t="str">
-        <v>渝北区</v>
+        <v>观山湖区</v>
       </c>
     </row>
     <row r="98">
@@ -2064,7 +2064,7 @@
         <v>西南区域</v>
       </c>
       <c r="B98" t="str">
-        <v>猛士贵阳观山湖店</v>
+        <v>猛士贵阳花溪店</v>
       </c>
       <c r="C98" t="str">
         <v>贵州省</v>
@@ -2073,7 +2073,7 @@
         <v>贵阳市</v>
       </c>
       <c r="E98" t="str">
-        <v>观山湖区</v>
+        <v>花溪区</v>
       </c>
     </row>
     <row r="99">
@@ -2081,16 +2081,16 @@
         <v>西南区域</v>
       </c>
       <c r="B99" t="str">
-        <v>猛士贵阳花溪店</v>
+        <v>猛士遵义汇川区店</v>
       </c>
       <c r="C99" t="str">
         <v>贵州省</v>
       </c>
       <c r="D99" t="str">
-        <v>贵阳市</v>
+        <v>遵义市</v>
       </c>
       <c r="E99" t="str">
-        <v>花溪区</v>
+        <v>汇川区</v>
       </c>
     </row>
     <row r="100">
@@ -2098,16 +2098,16 @@
         <v>西南区域</v>
       </c>
       <c r="B100" t="str">
-        <v>猛士遵义汇川区店</v>
+        <v>猛士成都天府新区店</v>
       </c>
       <c r="C100" t="str">
-        <v>贵州省</v>
+        <v>四川省</v>
       </c>
       <c r="D100" t="str">
-        <v>遵义市</v>
+        <v>成都市</v>
       </c>
       <c r="E100" t="str">
-        <v>汇川区</v>
+        <v>双流区</v>
       </c>
     </row>
     <row r="101">
@@ -2115,7 +2115,7 @@
         <v>西南区域</v>
       </c>
       <c r="B101" t="str">
-        <v>猛士成都天府新区店</v>
+        <v>猛士成都武侯区店</v>
       </c>
       <c r="C101" t="str">
         <v>四川省</v>
@@ -2124,7 +2124,7 @@
         <v>成都市</v>
       </c>
       <c r="E101" t="str">
-        <v>双流区</v>
+        <v>武侯区</v>
       </c>
     </row>
     <row r="102">
@@ -2132,16 +2132,16 @@
         <v>西南区域</v>
       </c>
       <c r="B102" t="str">
-        <v>猛士成都武侯区店</v>
+        <v>猛士乐山高新店</v>
       </c>
       <c r="C102" t="str">
         <v>四川省</v>
       </c>
       <c r="D102" t="str">
-        <v>成都市</v>
+        <v>乐山市</v>
       </c>
       <c r="E102" t="str">
-        <v>武侯区</v>
+        <v>市中区</v>
       </c>
     </row>
     <row r="103">
@@ -2149,16 +2149,16 @@
         <v>西南区域</v>
       </c>
       <c r="B103" t="str">
-        <v>猛士乐山高新店</v>
+        <v>猛士西昌安宁店</v>
       </c>
       <c r="C103" t="str">
         <v>四川省</v>
       </c>
       <c r="D103" t="str">
-        <v>乐山市</v>
+        <v>凉山彝族自治州</v>
       </c>
       <c r="E103" t="str">
-        <v>市中区</v>
+        <v>西昌市</v>
       </c>
     </row>
     <row r="104">
@@ -2166,16 +2166,16 @@
         <v>西南区域</v>
       </c>
       <c r="B104" t="str">
-        <v>猛士西昌安宁店</v>
+        <v>猛士泸州龙马潭店</v>
       </c>
       <c r="C104" t="str">
         <v>四川省</v>
       </c>
       <c r="D104" t="str">
-        <v>凉山彝族自治州</v>
+        <v>泸州市</v>
       </c>
       <c r="E104" t="str">
-        <v>西昌市</v>
+        <v>龙马潭区</v>
       </c>
     </row>
     <row r="105">
@@ -2183,16 +2183,16 @@
         <v>西南区域</v>
       </c>
       <c r="B105" t="str">
-        <v>猛士泸州龙马潭店</v>
+        <v>猛士眉山东坡店</v>
       </c>
       <c r="C105" t="str">
         <v>四川省</v>
       </c>
       <c r="D105" t="str">
-        <v>泸州市</v>
+        <v>眉山市</v>
       </c>
       <c r="E105" t="str">
-        <v>龙马潭区</v>
+        <v>东坡区</v>
       </c>
     </row>
     <row r="106">
@@ -2200,16 +2200,16 @@
         <v>西南区域</v>
       </c>
       <c r="B106" t="str">
-        <v>猛士眉山东坡店</v>
+        <v>猛士绵阳涪城店</v>
       </c>
       <c r="C106" t="str">
         <v>四川省</v>
       </c>
       <c r="D106" t="str">
-        <v>眉山市</v>
+        <v>绵阳市</v>
       </c>
       <c r="E106" t="str">
-        <v>东坡区</v>
+        <v>涪城区</v>
       </c>
     </row>
     <row r="107">
@@ -2217,16 +2217,16 @@
         <v>西南区域</v>
       </c>
       <c r="B107" t="str">
-        <v>猛士绵阳涪城店</v>
+        <v>猛士南充高坪店</v>
       </c>
       <c r="C107" t="str">
         <v>四川省</v>
       </c>
       <c r="D107" t="str">
-        <v>绵阳市</v>
+        <v>南充市</v>
       </c>
       <c r="E107" t="str">
-        <v>涪城区</v>
+        <v>高坪区</v>
       </c>
     </row>
     <row r="108">
@@ -2234,16 +2234,16 @@
         <v>西南区域</v>
       </c>
       <c r="B108" t="str">
-        <v>猛士南充高坪店</v>
+        <v>猛士攀枝花天骏店</v>
       </c>
       <c r="C108" t="str">
         <v>四川省</v>
       </c>
       <c r="D108" t="str">
-        <v>南充市</v>
+        <v>攀枝花市</v>
       </c>
       <c r="E108" t="str">
-        <v>高坪区</v>
+        <v>西区</v>
       </c>
     </row>
     <row r="109">
@@ -2251,16 +2251,16 @@
         <v>西南区域</v>
       </c>
       <c r="B109" t="str">
-        <v>猛士攀枝花天骏店</v>
+        <v>猛士宜宾临港店</v>
       </c>
       <c r="C109" t="str">
         <v>四川省</v>
       </c>
       <c r="D109" t="str">
-        <v>攀枝花市</v>
+        <v>宜宾市</v>
       </c>
       <c r="E109" t="str">
-        <v>西区</v>
+        <v>翠屏区</v>
       </c>
     </row>
     <row r="110">
@@ -2268,16 +2268,16 @@
         <v>西南区域</v>
       </c>
       <c r="B110" t="str">
-        <v>猛士宜宾临港店</v>
+        <v>猛士拉萨城关区店</v>
       </c>
       <c r="C110" t="str">
-        <v>四川省</v>
+        <v>西藏自治区</v>
       </c>
       <c r="D110" t="str">
-        <v>宜宾市</v>
+        <v>拉萨市</v>
       </c>
       <c r="E110" t="str">
-        <v>翠屏区</v>
+        <v>城关区</v>
       </c>
     </row>
     <row r="111">
@@ -2285,16 +2285,16 @@
         <v>西南区域</v>
       </c>
       <c r="B111" t="str">
-        <v>猛士拉萨城关区店</v>
+        <v>猛士林芝巴宜区店</v>
       </c>
       <c r="C111" t="str">
         <v>西藏自治区</v>
       </c>
       <c r="D111" t="str">
-        <v>拉萨市</v>
+        <v>林芝市</v>
       </c>
       <c r="E111" t="str">
-        <v>城关区</v>
+        <v>巴宜区</v>
       </c>
     </row>
     <row r="112">
@@ -2302,16 +2302,16 @@
         <v>西南区域</v>
       </c>
       <c r="B112" t="str">
-        <v>猛士林芝巴宜区店</v>
+        <v>猛士大理店</v>
       </c>
       <c r="C112" t="str">
-        <v>西藏自治区</v>
+        <v>云南省</v>
       </c>
       <c r="D112" t="str">
-        <v>林芝市</v>
+        <v>大理白族自治州</v>
       </c>
       <c r="E112" t="str">
-        <v>巴宜区</v>
+        <v>大理市</v>
       </c>
     </row>
     <row r="113">
@@ -2319,16 +2319,16 @@
         <v>西南区域</v>
       </c>
       <c r="B113" t="str">
-        <v>猛士大理店</v>
+        <v>猛士昆明西山店</v>
       </c>
       <c r="C113" t="str">
         <v>云南省</v>
       </c>
       <c r="D113" t="str">
-        <v>大理白族自治州</v>
+        <v>昆明市</v>
       </c>
       <c r="E113" t="str">
-        <v>大理市</v>
+        <v>西山区</v>
       </c>
     </row>
     <row r="114">
@@ -2336,33 +2336,33 @@
         <v>西南区域</v>
       </c>
       <c r="B114" t="str">
-        <v>猛士昆明西山店</v>
+        <v>猛士西双版纳景洪店</v>
       </c>
       <c r="C114" t="str">
         <v>云南省</v>
       </c>
       <c r="D114" t="str">
-        <v>昆明市</v>
+        <v>西双版纳傣族自治州</v>
       </c>
       <c r="E114" t="str">
-        <v>西山区</v>
+        <v>景洪市</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>西南区域</v>
+        <v>西北区域</v>
       </c>
       <c r="B115" t="str">
-        <v>猛士西双版纳景洪店</v>
+        <v>猛士敦煌店</v>
       </c>
       <c r="C115" t="str">
-        <v>云南省</v>
+        <v>甘肃省</v>
       </c>
       <c r="D115" t="str">
-        <v>西双版纳傣族自治州</v>
+        <v>酒泉市</v>
       </c>
       <c r="E115" t="str">
-        <v>景洪市</v>
+        <v>敦煌市</v>
       </c>
     </row>
     <row r="116">
@@ -2370,16 +2370,16 @@
         <v>西北区域</v>
       </c>
       <c r="B116" t="str">
-        <v>猛士敦煌店</v>
+        <v>猛士兰州安宁店</v>
       </c>
       <c r="C116" t="str">
         <v>甘肃省</v>
       </c>
       <c r="D116" t="str">
-        <v>酒泉市</v>
+        <v>兰州市</v>
       </c>
       <c r="E116" t="str">
-        <v>敦煌市</v>
+        <v>安宁区</v>
       </c>
     </row>
     <row r="117">
@@ -2387,16 +2387,16 @@
         <v>西北区域</v>
       </c>
       <c r="B117" t="str">
-        <v>猛士兰州安宁店</v>
+        <v>猛士庆阳西峰区店</v>
       </c>
       <c r="C117" t="str">
         <v>甘肃省</v>
       </c>
       <c r="D117" t="str">
-        <v>兰州市</v>
+        <v>庆阳市</v>
       </c>
       <c r="E117" t="str">
-        <v>安宁区</v>
+        <v>西峰区</v>
       </c>
     </row>
     <row r="118">
@@ -2404,16 +2404,16 @@
         <v>西北区域</v>
       </c>
       <c r="B118" t="str">
-        <v>猛士庆阳西峰区店</v>
+        <v>猛士银川德胜店</v>
       </c>
       <c r="C118" t="str">
-        <v>甘肃省</v>
+        <v>宁夏回族自治区</v>
       </c>
       <c r="D118" t="str">
-        <v>庆阳市</v>
+        <v>银川市</v>
       </c>
       <c r="E118" t="str">
-        <v>西峰区</v>
+        <v>贺兰县</v>
       </c>
     </row>
     <row r="119">
@@ -2421,16 +2421,16 @@
         <v>西北区域</v>
       </c>
       <c r="B119" t="str">
-        <v>猛士银川德胜店</v>
+        <v>猛士西宁城东店</v>
       </c>
       <c r="C119" t="str">
-        <v>宁夏回族自治区</v>
+        <v>青海省</v>
       </c>
       <c r="D119" t="str">
-        <v>银川市</v>
+        <v>西宁市</v>
       </c>
       <c r="E119" t="str">
-        <v>贺兰县</v>
+        <v>城东区</v>
       </c>
     </row>
     <row r="120">
@@ -2438,16 +2438,16 @@
         <v>西北区域</v>
       </c>
       <c r="B120" t="str">
-        <v>猛士西宁城东店</v>
+        <v>猛士宝鸡平安路店</v>
       </c>
       <c r="C120" t="str">
-        <v>青海省</v>
+        <v>陕西省</v>
       </c>
       <c r="D120" t="str">
-        <v>西宁市</v>
+        <v>宝鸡市</v>
       </c>
       <c r="E120" t="str">
-        <v>城东区</v>
+        <v>渭滨区</v>
       </c>
     </row>
     <row r="121">
@@ -2455,16 +2455,16 @@
         <v>西北区域</v>
       </c>
       <c r="B121" t="str">
-        <v>猛士宝鸡平安路店</v>
+        <v>猛士西安浐灞店</v>
       </c>
       <c r="C121" t="str">
         <v>陕西省</v>
       </c>
       <c r="D121" t="str">
-        <v>宝鸡市</v>
+        <v>西安市</v>
       </c>
       <c r="E121" t="str">
-        <v>渭滨区</v>
+        <v>灞桥区</v>
       </c>
     </row>
     <row r="122">
@@ -2472,7 +2472,7 @@
         <v>西北区域</v>
       </c>
       <c r="B122" t="str">
-        <v>猛士西安浐灞店</v>
+        <v>猛士西安未央店</v>
       </c>
       <c r="C122" t="str">
         <v>陕西省</v>
@@ -2481,7 +2481,7 @@
         <v>西安市</v>
       </c>
       <c r="E122" t="str">
-        <v>灞桥区</v>
+        <v>未央区</v>
       </c>
     </row>
     <row r="123">
@@ -2489,7 +2489,7 @@
         <v>西北区域</v>
       </c>
       <c r="B123" t="str">
-        <v>猛士西安未央店</v>
+        <v>猛士西安经开店</v>
       </c>
       <c r="C123" t="str">
         <v>陕西省</v>
@@ -2506,16 +2506,16 @@
         <v>西北区域</v>
       </c>
       <c r="B124" t="str">
-        <v>猛士西安经开店</v>
+        <v>猛士榆林草海则店</v>
       </c>
       <c r="C124" t="str">
         <v>陕西省</v>
       </c>
       <c r="D124" t="str">
-        <v>西安市</v>
+        <v>榆林市</v>
       </c>
       <c r="E124" t="str">
-        <v>未央区</v>
+        <v>横山区</v>
       </c>
     </row>
     <row r="125">
@@ -2523,16 +2523,16 @@
         <v>西北区域</v>
       </c>
       <c r="B125" t="str">
-        <v>猛士榆林草海则店</v>
+        <v>猛士乌鲁木齐店</v>
       </c>
       <c r="C125" t="str">
-        <v>陕西省</v>
+        <v>新疆维吾尔自治区</v>
       </c>
       <c r="D125" t="str">
-        <v>榆林市</v>
+        <v>乌鲁木齐市</v>
       </c>
       <c r="E125" t="str">
-        <v>横山区</v>
+        <v>水磨沟区</v>
       </c>
     </row>
     <row r="126">
@@ -2540,7 +2540,7 @@
         <v>西北区域</v>
       </c>
       <c r="B126" t="str">
-        <v>猛士乌鲁木齐店</v>
+        <v>猛士乌鲁木齐喀什西路店</v>
       </c>
       <c r="C126" t="str">
         <v>新疆维吾尔自治区</v>
@@ -2549,24 +2549,24 @@
         <v>乌鲁木齐市</v>
       </c>
       <c r="E126" t="str">
-        <v>水磨沟区</v>
+        <v>头屯河区</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>西北区域</v>
+        <v>东北区域</v>
       </c>
       <c r="B127" t="str">
-        <v>猛士乌鲁木齐喀什西路店</v>
+        <v>猛士大庆让胡路区店</v>
       </c>
       <c r="C127" t="str">
-        <v>新疆维吾尔自治区</v>
+        <v>黑龙江省</v>
       </c>
       <c r="D127" t="str">
-        <v>乌鲁木齐市</v>
+        <v>大庆市</v>
       </c>
       <c r="E127" t="str">
-        <v>头屯河区</v>
+        <v>让胡路区</v>
       </c>
     </row>
     <row r="128">
@@ -2574,16 +2574,16 @@
         <v>东北区域</v>
       </c>
       <c r="B128" t="str">
-        <v>猛士大庆让胡路区店</v>
+        <v>猛士哈尔滨香坊店</v>
       </c>
       <c r="C128" t="str">
         <v>黑龙江省</v>
       </c>
       <c r="D128" t="str">
-        <v>大庆市</v>
+        <v>哈尔滨市</v>
       </c>
       <c r="E128" t="str">
-        <v>让胡路区</v>
+        <v>香坊区</v>
       </c>
     </row>
     <row r="129">
@@ -2591,16 +2591,16 @@
         <v>东北区域</v>
       </c>
       <c r="B129" t="str">
-        <v>猛士哈尔滨香坊店</v>
+        <v>猛士北安店</v>
       </c>
       <c r="C129" t="str">
         <v>黑龙江省</v>
       </c>
       <c r="D129" t="str">
-        <v>哈尔滨市</v>
+        <v>黑河市</v>
       </c>
       <c r="E129" t="str">
-        <v>香坊区</v>
+        <v>北安市</v>
       </c>
     </row>
     <row r="130">
@@ -2608,16 +2608,16 @@
         <v>东北区域</v>
       </c>
       <c r="B130" t="str">
-        <v>猛士北安店</v>
+        <v>猛士佳木斯郊区店</v>
       </c>
       <c r="C130" t="str">
         <v>黑龙江省</v>
       </c>
       <c r="D130" t="str">
-        <v>黑河市</v>
+        <v>佳木斯市</v>
       </c>
       <c r="E130" t="str">
-        <v>北安市</v>
+        <v>郊区</v>
       </c>
     </row>
     <row r="131">
@@ -2625,16 +2625,16 @@
         <v>东北区域</v>
       </c>
       <c r="B131" t="str">
-        <v>猛士佳木斯郊区店</v>
+        <v>猛士牡丹江阳明区店</v>
       </c>
       <c r="C131" t="str">
         <v>黑龙江省</v>
       </c>
       <c r="D131" t="str">
-        <v>佳木斯市</v>
+        <v>牡丹江市</v>
       </c>
       <c r="E131" t="str">
-        <v>郊区</v>
+        <v>阳明区</v>
       </c>
     </row>
     <row r="132">
@@ -2642,16 +2642,16 @@
         <v>东北区域</v>
       </c>
       <c r="B132" t="str">
-        <v>猛士牡丹江阳明区店</v>
+        <v>猛士齐齐哈尔铁锋区店</v>
       </c>
       <c r="C132" t="str">
         <v>黑龙江省</v>
       </c>
       <c r="D132" t="str">
-        <v>牡丹江市</v>
+        <v>齐齐哈尔市</v>
       </c>
       <c r="E132" t="str">
-        <v>阳明区</v>
+        <v>铁锋区</v>
       </c>
     </row>
     <row r="133">
@@ -2659,16 +2659,16 @@
         <v>东北区域</v>
       </c>
       <c r="B133" t="str">
-        <v>猛士齐齐哈尔铁锋区店</v>
+        <v>猛士松原宁江区店</v>
       </c>
       <c r="C133" t="str">
-        <v>黑龙江省</v>
+        <v>吉林省</v>
       </c>
       <c r="D133" t="str">
-        <v>齐齐哈尔市</v>
+        <v>松原市</v>
       </c>
       <c r="E133" t="str">
-        <v>铁锋区</v>
+        <v>宁江区</v>
       </c>
     </row>
     <row r="134">
@@ -2676,16 +2676,16 @@
         <v>东北区域</v>
       </c>
       <c r="B134" t="str">
-        <v>猛士松原宁江区店</v>
+        <v>猛士长春经开店</v>
       </c>
       <c r="C134" t="str">
         <v>吉林省</v>
       </c>
       <c r="D134" t="str">
-        <v>松原市</v>
+        <v>长春市</v>
       </c>
       <c r="E134" t="str">
-        <v>宁江区</v>
+        <v>二道区</v>
       </c>
     </row>
     <row r="135">
@@ -2693,16 +2693,16 @@
         <v>东北区域</v>
       </c>
       <c r="B135" t="str">
-        <v>猛士长春经开店</v>
+        <v>猛士大连华北路店</v>
       </c>
       <c r="C135" t="str">
-        <v>吉林省</v>
+        <v>辽宁省</v>
       </c>
       <c r="D135" t="str">
-        <v>长春市</v>
+        <v>大连市</v>
       </c>
       <c r="E135" t="str">
-        <v>二道区</v>
+        <v>甘井子区</v>
       </c>
     </row>
     <row r="136">
@@ -2710,16 +2710,16 @@
         <v>东北区域</v>
       </c>
       <c r="B136" t="str">
-        <v>猛士大连华北路店</v>
+        <v>猛士沈阳店</v>
       </c>
       <c r="C136" t="str">
         <v>辽宁省</v>
       </c>
       <c r="D136" t="str">
-        <v>大连市</v>
+        <v>沈阳市</v>
       </c>
       <c r="E136" t="str">
-        <v>甘井子区</v>
+        <v>浑南区</v>
       </c>
     </row>
     <row r="137">
@@ -2727,7 +2727,7 @@
         <v>东北区域</v>
       </c>
       <c r="B137" t="str">
-        <v>猛士沈阳店</v>
+        <v>猛士沈阳沈河店</v>
       </c>
       <c r="C137" t="str">
         <v>辽宁省</v>
@@ -2736,7 +2736,7 @@
         <v>沈阳市</v>
       </c>
       <c r="E137" t="str">
-        <v>浑南区</v>
+        <v>沈河区</v>
       </c>
     </row>
     <row r="138">
@@ -2744,16 +2744,16 @@
         <v>东北区域</v>
       </c>
       <c r="B138" t="str">
-        <v>猛士沈阳沈河店</v>
+        <v>猛士包头九原店</v>
       </c>
       <c r="C138" t="str">
-        <v>辽宁省</v>
+        <v>内蒙古自治区</v>
       </c>
       <c r="D138" t="str">
-        <v>沈阳市</v>
+        <v>包头市</v>
       </c>
       <c r="E138" t="str">
-        <v>沈河区</v>
+        <v>九原区</v>
       </c>
     </row>
     <row r="139">
@@ -2761,16 +2761,16 @@
         <v>东北区域</v>
       </c>
       <c r="B139" t="str">
-        <v>猛士包头九原店</v>
+        <v>猛士赤峰红山店</v>
       </c>
       <c r="C139" t="str">
         <v>内蒙古自治区</v>
       </c>
       <c r="D139" t="str">
-        <v>包头市</v>
+        <v>赤峰市</v>
       </c>
       <c r="E139" t="str">
-        <v>九原区</v>
+        <v>红山区</v>
       </c>
     </row>
     <row r="140">
@@ -2778,16 +2778,16 @@
         <v>东北区域</v>
       </c>
       <c r="B140" t="str">
-        <v>猛士赤峰红山店</v>
+        <v>猛士鄂尔多斯东胜店</v>
       </c>
       <c r="C140" t="str">
         <v>内蒙古自治区</v>
       </c>
       <c r="D140" t="str">
-        <v>赤峰市</v>
+        <v>鄂尔多斯市</v>
       </c>
       <c r="E140" t="str">
-        <v>红山区</v>
+        <v>东胜区</v>
       </c>
     </row>
     <row r="141">
@@ -2795,16 +2795,16 @@
         <v>东北区域</v>
       </c>
       <c r="B141" t="str">
-        <v>猛士鄂尔多斯东胜店</v>
+        <v>猛士呼和浩特海西路店</v>
       </c>
       <c r="C141" t="str">
         <v>内蒙古自治区</v>
       </c>
       <c r="D141" t="str">
-        <v>鄂尔多斯市</v>
+        <v>呼和浩特市</v>
       </c>
       <c r="E141" t="str">
-        <v>东胜区</v>
+        <v>回民区</v>
       </c>
     </row>
     <row r="142">
@@ -2812,16 +2812,16 @@
         <v>东北区域</v>
       </c>
       <c r="B142" t="str">
-        <v>猛士呼和浩特海西路店</v>
+        <v>猛士呼伦贝尔汽车城店</v>
       </c>
       <c r="C142" t="str">
         <v>内蒙古自治区</v>
       </c>
       <c r="D142" t="str">
-        <v>呼和浩特市</v>
+        <v>呼伦贝尔市</v>
       </c>
       <c r="E142" t="str">
-        <v>回民区</v>
+        <v>鄂温克族自治旗</v>
       </c>
     </row>
     <row r="143">
@@ -2829,16 +2829,16 @@
         <v>东北区域</v>
       </c>
       <c r="B143" t="str">
-        <v>猛士呼伦贝尔汽车城店</v>
+        <v>猛士通辽万林店</v>
       </c>
       <c r="C143" t="str">
         <v>内蒙古自治区</v>
       </c>
       <c r="D143" t="str">
-        <v>呼伦贝尔市</v>
+        <v>通辽市</v>
       </c>
       <c r="E143" t="str">
-        <v>鄂温克族自治旗</v>
+        <v>科尔沁区</v>
       </c>
     </row>
     <row r="144">
@@ -2846,16 +2846,16 @@
         <v>东北区域</v>
       </c>
       <c r="B144" t="str">
-        <v>猛士通辽万林店</v>
+        <v>猛士大同经开店</v>
       </c>
       <c r="C144" t="str">
-        <v>内蒙古自治区</v>
+        <v>山西省</v>
       </c>
       <c r="D144" t="str">
-        <v>通辽市</v>
+        <v>大同市</v>
       </c>
       <c r="E144" t="str">
-        <v>科尔沁区</v>
+        <v>云州区</v>
       </c>
     </row>
     <row r="145">
@@ -2863,16 +2863,16 @@
         <v>东北区域</v>
       </c>
       <c r="B145" t="str">
-        <v>猛士大同经开店</v>
+        <v>猛士晋城路宝店</v>
       </c>
       <c r="C145" t="str">
         <v>山西省</v>
       </c>
       <c r="D145" t="str">
-        <v>大同市</v>
+        <v>晋城市</v>
       </c>
       <c r="E145" t="str">
-        <v>云州区</v>
+        <v>泽州县</v>
       </c>
     </row>
     <row r="146">
@@ -2880,16 +2880,16 @@
         <v>东北区域</v>
       </c>
       <c r="B146" t="str">
-        <v>猛士晋城路宝店</v>
+        <v>猛士太原龙城店</v>
       </c>
       <c r="C146" t="str">
         <v>山西省</v>
       </c>
       <c r="D146" t="str">
-        <v>晋城市</v>
+        <v>太原市</v>
       </c>
       <c r="E146" t="str">
-        <v>泽州县</v>
+        <v>小店区</v>
       </c>
     </row>
     <row r="147">
@@ -2897,38 +2897,21 @@
         <v>东北区域</v>
       </c>
       <c r="B147" t="str">
-        <v>猛士太原龙城店</v>
+        <v>猛士长治潞州店</v>
       </c>
       <c r="C147" t="str">
         <v>山西省</v>
       </c>
       <c r="D147" t="str">
-        <v>太原市</v>
+        <v>长治市</v>
       </c>
       <c r="E147" t="str">
-        <v>小店区</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="str">
-        <v>东北区域</v>
-      </c>
-      <c r="B148" t="str">
-        <v>猛士长治潞州店</v>
-      </c>
-      <c r="C148" t="str">
-        <v>山西省</v>
-      </c>
-      <c r="D148" t="str">
-        <v>长治市</v>
-      </c>
-      <c r="E148" t="str">
         <v>潞州区</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E148"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E147"/>
   </ignoredErrors>
 </worksheet>
 </file>